--- a/cotacoes/2026-09-08/fechamento/PEDIDO_NAZARIA_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_NAZARIA_09-09-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -576,30 +576,30 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>630901</v>
+        <v>598071</v>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>7896064487016</t>
+          <t>7891010704780</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ABS GERIAMAX POS PARTO C/20UN</t>
+          <t>ABS SL ADAPT PLUS SUAVE ABAS C/32UN</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>20.88</v>
+        <v>18.57</v>
       </c>
       <c r="I2" s="5">
         <f>G2*H2</f>
@@ -610,13 +610,13 @@
         <v/>
       </c>
       <c r="K2" s="5" t="n">
-        <v>20.02</v>
+        <v>17.5267</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>17.35</v>
+        <v>17.5267</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>19.13</v>
+        <v>17.5267</v>
       </c>
       <c r="N2" s="6">
         <f>J2/M2-1</f>
@@ -628,7 +628,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.3% (aceito, lim 5%)</t>
+          <t>REAJUSTE +6.0% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.6% (aceito, lim 5%)</t>
+          <t>REAJUSTE +4.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.6% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1488,30 +1488,30 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>637261</v>
+        <v>576441</v>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>7899706159272</t>
+          <t>7891150045347</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CERAVE LOCAO HIDRATANTE 473ML-DEMAIS PROD</t>
+          <t>CONDIC.DOVE BABY CAB.CLA.200M</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>113.43</v>
+        <v>14.9</v>
       </c>
       <c r="I18" s="5">
         <f>G18*H18</f>
@@ -1522,13 +1522,13 @@
         <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>103.71</v>
+        <v>14.97</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>89.84</v>
+        <v>14.97</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>99.08666666666666</v>
+        <v>14.97</v>
       </c>
       <c r="N18" s="6">
         <f>J18/M18-1</f>
@@ -1540,37 +1540,37 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +9.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>614901</v>
+        <v>1943</v>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7891150001077</t>
+          <t>7891150086210</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CLEAR AT-C SH 200ML MEN QUEDA CONTROL M3</t>
+          <t>CR D CLOSE UP GEL MENTA 130G</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>15.7</v>
+        <v>3.87</v>
       </c>
       <c r="I19" s="5">
         <f>G19*H19</f>
@@ -1581,13 +1581,13 @@
         <v/>
       </c>
       <c r="K19" s="5" t="n">
-        <v>14.9942</v>
+        <v>3.86</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>14.0525</v>
+        <v>3.86</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>14.67223333333333</v>
+        <v>3.86</v>
       </c>
       <c r="N19" s="6">
         <f>J19/M19-1</f>
@@ -1599,37 +1599,37 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.7% (aceito, lim 5%)</t>
+          <t>REAJUSTE +0.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>616601</v>
+        <v>637691</v>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>7896000724748</t>
+          <t>7891150094949</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>COL P COR&amp;TON MEGA COLORS 12111 L S PLA</t>
+          <t>CR TRAT DOVE HIDRATACAO 270G</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>12.87</v>
+        <v>34.7</v>
       </c>
       <c r="I20" s="5">
         <f>G20*H20</f>
@@ -1640,13 +1640,13 @@
         <v/>
       </c>
       <c r="K20" s="5" t="n">
-        <v>12.09</v>
+        <v>40.79</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>10.5</v>
+        <v>40.79</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>11.56</v>
+        <v>40.79</v>
       </c>
       <c r="N20" s="6">
         <f>J20/M20-1</f>
@@ -1658,37 +1658,37 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.5% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>576441</v>
+        <v>653591</v>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>7891150045347</t>
+          <t>7896438200906</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CONDIC.DOVE BABY CAB.CLA.200M</t>
+          <t>CREATINA PROBIOTICA 300G</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>14.9</v>
+        <v>40.37</v>
       </c>
       <c r="I21" s="5">
         <f>G21*H21</f>
@@ -1699,13 +1699,13 @@
         <v/>
       </c>
       <c r="K21" s="5" t="n">
-        <v>14.97</v>
+        <v>40.37</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>14.97</v>
+        <v>40.37</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>14.97</v>
+        <v>40.37</v>
       </c>
       <c r="N21" s="6">
         <f>J21/M21-1</f>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1943</v>
+        <v>630671</v>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>7891150086210</t>
+          <t>7898108640746</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CR D CLOSE UP GEL MENTA 130G</t>
+          <t>CURATIVO CICATRISAN KURA DODOI CX 20 UND</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>3.87</v>
+        <v>5.016</v>
       </c>
       <c r="I22" s="5">
         <f>G22*H22</f>
@@ -1758,13 +1758,13 @@
         <v/>
       </c>
       <c r="K22" s="5" t="n">
-        <v>3.86</v>
+        <v>5.42</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3.86</v>
+        <v>5.42</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>3.86</v>
+        <v>5.419999999999999</v>
       </c>
       <c r="N22" s="6">
         <f>J22/M22-1</f>
@@ -1776,37 +1776,37 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.3% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>672041</v>
+        <v>833</v>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>7908966528534</t>
+          <t>7891800540406</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CR PENT ELSEVE COLAGENO 250ML-DEMAIS PROD</t>
+          <t>CURATIVO CREMER MINIONS 10UN</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>15.92</v>
+        <v>4.462</v>
       </c>
       <c r="I23" s="5">
         <f>G23*H23</f>
@@ -1817,13 +1817,13 @@
         <v/>
       </c>
       <c r="K23" s="5" t="n">
-        <v>14.75</v>
+        <v>4.59</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>14.14</v>
+        <v>4.59</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>14.14</v>
+        <v>4.59</v>
       </c>
       <c r="N23" s="6">
         <f>J23/M23-1</f>
@@ -1835,37 +1835,37 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.9% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>637691</v>
+        <v>631611</v>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>7891150094949</t>
+          <t>7896544925496</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CR TRAT DOVE HIDRATACAO 270G</t>
+          <t>CURATIVO FLEXIVEL SHOW DA LUNA  C/10UN.</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>34.7</v>
+        <v>3.06</v>
       </c>
       <c r="I24" s="5">
         <f>G24*H24</f>
@@ -1876,13 +1876,13 @@
         <v/>
       </c>
       <c r="K24" s="5" t="n">
-        <v>40.79</v>
+        <v>3.06</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>40.79</v>
+        <v>3.06</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>40.79</v>
+        <v>3.06</v>
       </c>
       <c r="N24" s="6">
         <f>J24/M24-1</f>
@@ -1894,37 +1894,41 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (2 un)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>653591</v>
+        <v>669911</v>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>7896438200906</t>
+          <t>7891150100503</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CREATINA PROBIOTICA 300G</t>
+          <t>DEO REXONA WOMEN AER INV 150ML   UNIL %DN:12.00</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>40.37</v>
+        <v>15.18</v>
       </c>
       <c r="I25" s="5">
         <f>G25*H25</f>
@@ -1935,13 +1939,13 @@
         <v/>
       </c>
       <c r="K25" s="5" t="n">
-        <v>40.37</v>
+        <v>16.62</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>40.37</v>
+        <v>13.53</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>40.37</v>
+        <v>15.59</v>
       </c>
       <c r="N25" s="6">
         <f>J25/M25-1</f>
@@ -1953,24 +1957,24 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>630671</v>
+        <v>6581</v>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>7898108640746</t>
+          <t>7891268101799</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO CICATRISAN KURA DODOI CX 20 UND</t>
+          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -1983,7 +1987,7 @@
         <v>4</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>5.016</v>
+        <v>35.4825</v>
       </c>
       <c r="I26" s="5">
         <f>G26*H26</f>
@@ -1994,13 +1998,13 @@
         <v/>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5.42</v>
+        <v>36.87</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>5.42</v>
+        <v>33.56</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>5.419999999999999</v>
+        <v>34.68</v>
       </c>
       <c r="N26" s="6">
         <f>J26/M26-1</f>
@@ -2012,24 +2016,24 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>833</v>
+        <v>6601</v>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>7891800540406</t>
+          <t>7891268101782</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO CREMER MINIONS 10UN</t>
+          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML+1SER PREENCH</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2042,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>4.462</v>
+        <v>45.98</v>
       </c>
       <c r="I27" s="5">
         <f>G27*H27</f>
@@ -2053,13 +2057,13 @@
         <v/>
       </c>
       <c r="K27" s="5" t="n">
-        <v>4.59</v>
+        <v>46.77</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>4.59</v>
+        <v>41.6</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>4.59</v>
+        <v>43.87333333333333</v>
       </c>
       <c r="N27" s="6">
         <f>J27/M27-1</f>
@@ -2071,37 +2075,37 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>631611</v>
+        <v>645431</v>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>7896544925496</t>
+          <t>7891058018238</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO FLEXIVEL SHOW DA LUNA  C/10UN.</t>
+          <t>DERMACYD FEM 200+100ML</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>3.06</v>
+        <v>25.11</v>
       </c>
       <c r="I28" s="5">
         <f>G28*H28</f>
@@ -2112,13 +2116,13 @@
         <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>3.06</v>
+        <v>25.16</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>3.06</v>
+        <v>25.06</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>3.06</v>
+        <v>25.12666666666667</v>
       </c>
       <c r="N28" s="6">
         <f>J28/M28-1</f>
@@ -2130,41 +2134,41 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>estoque parcial (2 un)</t>
+          <t>estoque parcial (1 un)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>669911</v>
+        <v>591811</v>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>7891150100503</t>
+          <t>78924352</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DEO REXONA WOMEN AER INV 150ML   UNIL %DN:12.00</t>
+          <t>DES R-ON REXONA W.COTTON 50ML</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>15.18</v>
+        <v>8.27</v>
       </c>
       <c r="I29" s="5">
         <f>G29*H29</f>
@@ -2175,13 +2179,13 @@
         <v/>
       </c>
       <c r="K29" s="5" t="n">
-        <v>16.62</v>
+        <v>7.9967</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>13.53</v>
+        <v>7.9967</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>15.59</v>
+        <v>7.9967</v>
       </c>
       <c r="N29" s="6">
         <f>J29/M29-1</f>
@@ -2193,37 +2197,37 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6581</v>
+        <v>539561</v>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>7891268101799</t>
+          <t>7891106913966</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML</t>
+          <t>DIANE 35 2+0,035MG CX 21 DRG</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>35.4825</v>
+        <v>31.1904</v>
       </c>
       <c r="I30" s="5">
         <f>G30*H30</f>
@@ -2234,13 +2238,13 @@
         <v/>
       </c>
       <c r="K30" s="5" t="n">
-        <v>36.87</v>
+        <v>32.08</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>33.56</v>
+        <v>27.875</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>34.68</v>
+        <v>30.225</v>
       </c>
       <c r="N30" s="6">
         <f>J30/M30-1</f>
@@ -2259,17 +2263,17 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6601</v>
+        <v>648781</v>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>7891268101782</t>
+          <t>7891150021662</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML+1SER PREENCH</t>
+          <t>DOVE SH 200ML MEN 2EM1 FORCA RESISTEN M3</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -2282,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>45.98</v>
+        <v>15.97</v>
       </c>
       <c r="I31" s="5">
         <f>G31*H31</f>
@@ -2293,13 +2297,13 @@
         <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>46.77</v>
+        <v>15.4</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>41.6</v>
+        <v>15.4</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>43.87333333333333</v>
+        <v>15.4</v>
       </c>
       <c r="N31" s="6">
         <f>J31/M31-1</f>
@@ -2311,37 +2315,37 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>645431</v>
+        <v>648591</v>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>7891058018238</t>
+          <t>7891150021709</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DERMACYD FEM 200+100ML</t>
+          <t>DOVE SH 200ML MEN PROTECAO ANTICASPA M3</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>25.11</v>
+        <v>15.97</v>
       </c>
       <c r="I32" s="5">
         <f>G32*H32</f>
@@ -2352,13 +2356,13 @@
         <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>25.16</v>
+        <v>15.4</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>25.06</v>
+        <v>15.4</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>25.12666666666667</v>
+        <v>15.4</v>
       </c>
       <c r="N32" s="6">
         <f>J32/M32-1</f>
@@ -2370,28 +2374,24 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un)</t>
-        </is>
-      </c>
+          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>591811</v>
+        <v>452521</v>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>78924352</t>
+          <t>7898109240136</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DES R-ON REXONA W.COTTON 50ML</t>
+          <t>ELOTIN SOL OTO FR GTS 5ML</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2404,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>8.27</v>
+        <v>9.490500000000001</v>
       </c>
       <c r="I33" s="5">
         <f>G33*H33</f>
@@ -2415,13 +2415,13 @@
         <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>7.9967</v>
+        <v>8.99</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>7.9967</v>
+        <v>8.99</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>7.9967</v>
+        <v>8.99</v>
       </c>
       <c r="N33" s="6">
         <f>J33/M33-1</f>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.4% (aceito, lim 5%)</t>
+          <t>REAJUSTE +5.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>539561</v>
+        <v>594331</v>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>7891106913966</t>
+          <t>070942005111</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DIANE 35 2+0,035MG CX 21 DRG</t>
+          <t>ESC INTERDENTAL GUMSOFT PICK</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>31.1904</v>
+        <v>21.5616</v>
       </c>
       <c r="I34" s="5">
         <f>G34*H34</f>
@@ -2474,13 +2474,13 @@
         <v/>
       </c>
       <c r="K34" s="5" t="n">
-        <v>32.08</v>
+        <v>21.99</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>27.875</v>
+        <v>21.99</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>30.225</v>
+        <v>21.99</v>
       </c>
       <c r="N34" s="6">
         <f>J34/M34-1</f>
@@ -2495,21 +2495,25 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>preços divergentes entre EANs (usado menor)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>648781</v>
+        <v>702501</v>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>7891150021662</t>
+          <t>7899026415478</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DOVE SH 200ML MEN 2EM1 FORCA RESISTEN M3</t>
+          <t>ESM COL_CREM JABUTICABA</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -2522,7 +2526,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>15.97</v>
+        <v>5.35</v>
       </c>
       <c r="I35" s="5">
         <f>G35*H35</f>
@@ -2533,13 +2537,13 @@
         <v/>
       </c>
       <c r="K35" s="5" t="n">
-        <v>15.4</v>
+        <v>5.93</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>15.4</v>
+        <v>5.93</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>15.4</v>
+        <v>5.93</v>
       </c>
       <c r="N35" s="6">
         <f>J35/M35-1</f>
@@ -2551,37 +2555,37 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.7% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>648591</v>
+        <v>235621</v>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>7891150021709</t>
+          <t>7894916510202</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DOVE SH 200ML MEN PROTECAO ANTICASPA M3</t>
+          <t>ESOGASTRO IBP KIT 14ESO 14CLA 28AMOX+28ESO-S</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>15.97</v>
+        <v>272.07375</v>
       </c>
       <c r="I36" s="5">
         <f>G36*H36</f>
@@ -2592,13 +2596,13 @@
         <v/>
       </c>
       <c r="K36" s="5" t="n">
-        <v>15.4</v>
+        <v>272.59</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>15.4</v>
+        <v>242.54</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>15.4</v>
+        <v>261.6066666666666</v>
       </c>
       <c r="N36" s="6">
         <f>J36/M36-1</f>
@@ -2610,37 +2614,37 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.7% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>452521</v>
+        <v>651561</v>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>7898109240136</t>
+          <t>7891800669299</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ELOTIN SOL OTO FR GTS 5ML</t>
+          <t>ESPARADRAPO CREMER BEGE 1,2CMX3M   CREM %DN:11.00</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>9.490500000000001</v>
+        <v>3.492</v>
       </c>
       <c r="I37" s="5">
         <f>G37*H37</f>
@@ -2651,13 +2655,13 @@
         <v/>
       </c>
       <c r="K37" s="5" t="n">
-        <v>8.99</v>
+        <v>3.59</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>8.99</v>
+        <v>3.59</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>8.99</v>
+        <v>3.59</v>
       </c>
       <c r="N37" s="6">
         <f>J37/M37-1</f>
@@ -2669,37 +2673,37 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>594331</v>
+        <v>578121</v>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>070942005111</t>
+          <t>7891800628432</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ESC INTERDENTAL GUMSOFT PICK</t>
+          <t>ESPARADRAPO SALVELOX 5CMX4,5M</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>21.5616</v>
+        <v>6.6542</v>
       </c>
       <c r="I38" s="5">
         <f>G38*H38</f>
@@ -2710,13 +2714,13 @@
         <v/>
       </c>
       <c r="K38" s="5" t="n">
-        <v>21.99</v>
+        <v>6.844</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>21.99</v>
+        <v>6.48</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>21.99</v>
+        <v>6.722666666666666</v>
       </c>
       <c r="N38" s="6">
         <f>J38/M38-1</f>
@@ -2728,41 +2732,37 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>preços divergentes entre EANs (usado menor)</t>
-        </is>
-      </c>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>702501</v>
+        <v>613831</v>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7899026415478</t>
+          <t>7896902234093</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ESM COL_CREM JABUTICABA</t>
+          <t>FARMAIODINE PVPI 10% 100ML</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>5.35</v>
+        <v>6.27</v>
       </c>
       <c r="I39" s="5">
         <f>G39*H39</f>
@@ -2773,13 +2773,13 @@
         <v/>
       </c>
       <c r="K39" s="5" t="n">
-        <v>5.93</v>
+        <v>7.09</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>5.93</v>
+        <v>7.09</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>5.93</v>
+        <v>7.09</v>
       </c>
       <c r="N39" s="6">
         <f>J39/M39-1</f>
@@ -2791,37 +2791,37 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>235621</v>
+        <v>430141</v>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>7894916510202</t>
+          <t>7896014673124</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ESOGASTRO IBP KIT 14ESO 14CLA 28AMOX+28ESO-S</t>
+          <t>FERROPURUM 20 MG/ML SOL INJ 5 AMP 5ML</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>272.07375</v>
+        <v>67.81409699999999</v>
       </c>
       <c r="I40" s="5">
         <f>G40*H40</f>
@@ -2832,13 +2832,13 @@
         <v/>
       </c>
       <c r="K40" s="5" t="n">
-        <v>272.59</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>242.54</v>
+        <v>51.6738</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>261.6066666666666</v>
+        <v>57.70143333333333</v>
       </c>
       <c r="N40" s="6">
         <f>J40/M40-1</f>
@@ -2857,30 +2857,30 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>651561</v>
+        <v>616361</v>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>7891800669299</t>
+          <t>7896523201504</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>ESPARADRAPO CREMER BEGE 1,2CMX3M   CREM %DN:11.00</t>
+          <t>FIGMED 200MG CAPS C/30</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>3.492</v>
+        <v>30.53</v>
       </c>
       <c r="I41" s="5">
         <f>G41*H41</f>
@@ -2891,13 +2891,13 @@
         <v/>
       </c>
       <c r="K41" s="5" t="n">
-        <v>3.59</v>
+        <v>35.69</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>3.59</v>
+        <v>31.99</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>3.59</v>
+        <v>33.83333333333333</v>
       </c>
       <c r="N41" s="6">
         <f>J41/M41-1</f>
@@ -2909,37 +2909,37 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>578121</v>
+        <v>249121</v>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>7891800628432</t>
+          <t>7896523227542</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ESPARADRAPO SALVELOX 5CMX4,5M</t>
+          <t>FINASTERIDA 1MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>6.6542</v>
+        <v>62.28</v>
       </c>
       <c r="I42" s="5">
         <f>G42*H42</f>
@@ -2949,56 +2949,44 @@
         <f>H42/E42</f>
         <v/>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>6.844</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>6.722666666666666</v>
-      </c>
-      <c r="N42" s="6">
-        <f>J42/M42-1</f>
-        <v/>
-      </c>
-      <c r="O42" s="6">
-        <f>J42/K42-1</f>
-        <v/>
-      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>613831</v>
+        <v>596631</v>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>7896902234093</t>
+          <t>7891800665529</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>FARMAIODINE PVPI 10% 100ML</t>
+          <t>FITA MICROPOROSA SALVELOX 1,2CMX4,5M</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>6.27</v>
+        <v>2.7257</v>
       </c>
       <c r="I43" s="5">
         <f>G43*H43</f>
@@ -3009,13 +2997,13 @@
         <v/>
       </c>
       <c r="K43" s="5" t="n">
-        <v>7.09</v>
+        <v>2.8038</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>7.09</v>
+        <v>2.65</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>7.09</v>
+        <v>2.752533333333333</v>
       </c>
       <c r="N43" s="6">
         <f>J43/M43-1</f>
@@ -3027,37 +3015,37 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>430141</v>
+        <v>614481</v>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>7896014673124</t>
+          <t>7896007551279</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>FERROPURUM 20 MG/ML SOL INJ 5 AMP 5ML</t>
+          <t>FRA HUGGIES CARE ROUP HIPER XXG C/48</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>67.81409699999999</v>
+        <v>89.83</v>
       </c>
       <c r="I44" s="5">
         <f>G44*H44</f>
@@ -3068,13 +3056,13 @@
         <v/>
       </c>
       <c r="K44" s="5" t="n">
-        <v>69.76000000000001</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>51.6738</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>57.70143333333333</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="N44" s="6">
         <f>J44/M44-1</f>
@@ -3086,37 +3074,37 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>616361</v>
+        <v>614451</v>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>7896523201504</t>
+          <t>7896007549719</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>FIGMED 200MG CAPS C/30</t>
+          <t>FRA HUGGIES SP CARE ROUP HIPER GDE C/60</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>30.53</v>
+        <v>89.83</v>
       </c>
       <c r="I45" s="5">
         <f>G45*H45</f>
@@ -3127,13 +3115,13 @@
         <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>35.69</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>31.99</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>33.83333333333333</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="N45" s="6">
         <f>J45/M45-1</f>
@@ -3145,24 +3133,24 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>249121</v>
+        <v>614461</v>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>7896523227542</t>
+          <t>7896007551262</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>FINASTERIDA 1MG CX 30 COMP REV</t>
+          <t>FRA HUGGIES SP CARE ROUP HIPER MED C/72</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -3175,7 +3163,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>62.28</v>
+        <v>89.83</v>
       </c>
       <c r="I46" s="5">
         <f>G46*H46</f>
@@ -3185,31 +3173,43 @@
         <f>H46/E46</f>
         <v/>
       </c>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="6" t="n"/>
-      <c r="O46" s="6" t="n"/>
+      <c r="K46" s="5" t="n">
+        <v>87.53619999999999</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>87.53619999999999</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>87.53619999999999</v>
+      </c>
+      <c r="N46" s="6">
+        <f>J46/M46-1</f>
+        <v/>
+      </c>
+      <c r="O46" s="6">
+        <f>J46/K46-1</f>
+        <v/>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>596631</v>
+        <v>617081</v>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>7891800665529</t>
+          <t>7896007553051</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>FITA MICROPOROSA SALVELOX 1,2CMX4,5M</t>
+          <t>FRA HUGGIES TRIPLA ROUP MEGA - GDE C/28</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -3222,7 +3222,7 @@
         <v>7</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>2.7257</v>
+        <v>37.88</v>
       </c>
       <c r="I47" s="5">
         <f>G47*H47</f>
@@ -3233,13 +3233,13 @@
         <v/>
       </c>
       <c r="K47" s="5" t="n">
-        <v>2.8038</v>
+        <v>36.98</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>2.65</v>
+        <v>36.98</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>2.752533333333333</v>
+        <v>36.98</v>
       </c>
       <c r="N47" s="6">
         <f>J47/M47-1</f>
@@ -3251,24 +3251,24 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>614481</v>
+        <v>616531</v>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>7896007551279</t>
+          <t>7896007553068</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES CARE ROUP HIPER XXG C/48</t>
+          <t>FRA HUGGIES TRIPLA ROUP MEGA - XG C/24</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -3281,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>89.83</v>
+        <v>37.88</v>
       </c>
       <c r="I48" s="5">
         <f>G48*H48</f>
@@ -3292,13 +3292,13 @@
         <v/>
       </c>
       <c r="K48" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="N48" s="6">
         <f>J48/M48-1</f>
@@ -3310,37 +3310,37 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>614451</v>
+        <v>572481</v>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>7896007549719</t>
+          <t>7896064486170</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES SP CARE ROUP HIPER GDE C/60</t>
+          <t>FRALDA GERIAMAX G 7 UN</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>89.83</v>
+        <v>16.36</v>
       </c>
       <c r="I49" s="5">
         <f>G49*H49</f>
@@ -3351,13 +3351,13 @@
         <v/>
       </c>
       <c r="K49" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="N49" s="6">
         <f>J49/M49-1</f>
@@ -3369,37 +3369,37 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>614461</v>
+        <v>572501</v>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>7896007551262</t>
+          <t>7896064486163</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES SP CARE ROUP HIPER MED C/72</t>
+          <t>FRALDA GERIAMAX M 8 UN</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>89.83</v>
+        <v>16.36</v>
       </c>
       <c r="I50" s="5">
         <f>G50*H50</f>
@@ -3410,13 +3410,13 @@
         <v/>
       </c>
       <c r="K50" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.26</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="N50" s="6">
         <f>J50/M50-1</f>
@@ -3428,37 +3428,37 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>617081</v>
+        <v>631061</v>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>7896007553051</t>
+          <t>7896007549269</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES TRIPLA ROUP MEGA - GDE C/28</t>
+          <t>FRALDA HUGGIES TRIPLA HIPER G 78UN</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>37.88</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="I51" s="5">
         <f>G51*H51</f>
@@ -3469,13 +3469,13 @@
         <v/>
       </c>
       <c r="K51" s="5" t="n">
-        <v>36.98</v>
+        <v>88.23</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>36.98</v>
+        <v>88.23</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>36.98</v>
+        <v>88.23</v>
       </c>
       <c r="N51" s="6">
         <f>J51/M51-1</f>
@@ -3487,37 +3487,37 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>616531</v>
+        <v>556021</v>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>7896007553068</t>
+          <t>7896007549702</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES TRIPLA ROUP MEGA - XG C/24</t>
+          <t>FRALDA SHORTINHO HUGGIES SUPREME CARE XXG 24UN</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>37.88</v>
+        <v>51.34</v>
       </c>
       <c r="I52" s="5">
         <f>G52*H52</f>
@@ -3528,13 +3528,13 @@
         <v/>
       </c>
       <c r="K52" s="5" t="n">
-        <v>36.98</v>
+        <v>50.0233</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>36.98</v>
+        <v>50.0233</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>36.98</v>
+        <v>50.0233</v>
       </c>
       <c r="N52" s="6">
         <f>J52/M52-1</f>
@@ -3546,37 +3546,37 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.4% (aceito, lim 5%)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>572481</v>
+        <v>670571</v>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>7896064486170</t>
+          <t>7898216368037</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>FRALDA GERIAMAX G 7 UN</t>
+          <t>GARDENAL 100MG C/20 COMP (C1)-REFERENCIA</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>16.36</v>
+        <v>9.468</v>
       </c>
       <c r="I53" s="5">
         <f>G53*H53</f>
@@ -3587,13 +3587,13 @@
         <v/>
       </c>
       <c r="K53" s="5" t="n">
-        <v>18.17</v>
+        <v>9.4094</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>18.17</v>
+        <v>9.4094</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>18.17</v>
+        <v>9.4094</v>
       </c>
       <c r="N53" s="6">
         <f>J53/M53-1</f>
@@ -3605,37 +3605,37 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>572501</v>
+        <v>630831</v>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>7896064486163</t>
+          <t>7899706178129</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>FRALDA GERIAMAX M 8 UN</t>
+          <t>GARNIER AGUA MICELAR 400ML TUDO EM 1</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>16.36</v>
+        <v>45.67</v>
       </c>
       <c r="I54" s="5">
         <f>G54*H54</f>
@@ -3646,13 +3646,13 @@
         <v/>
       </c>
       <c r="K54" s="5" t="n">
-        <v>18.26</v>
+        <v>44.69</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>18.17</v>
+        <v>44.69</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>18.17</v>
+        <v>44.69</v>
       </c>
       <c r="N54" s="6">
         <f>J54/M54-1</f>
@@ -3664,37 +3664,37 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +2.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>537821</v>
+        <v>189141</v>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>7896007549689</t>
+          <t>7891106003230</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES ROUPINHA SUPREME CARE - G - 30</t>
+          <t>GINO CANESTEN 20 MG/G CREME VAG BG 20G+3APLIC</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>51.34</v>
+        <v>73.19619999999999</v>
       </c>
       <c r="I55" s="5">
         <f>G55*H55</f>
@@ -3705,13 +3705,13 @@
         <v/>
       </c>
       <c r="K55" s="5" t="n">
-        <v>47.7</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>44.7033</v>
+        <v>65.23</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>46.7011</v>
+        <v>67.52166666666666</v>
       </c>
       <c r="N55" s="6">
         <f>J55/M55-1</f>
@@ -3723,37 +3723,37 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +3.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>631061</v>
+        <v>533121</v>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>7896007549269</t>
+          <t>7891721201806</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES TRIPLA HIPER G 78UN</t>
+          <t>GLIFAGE XR 500MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>86.56999999999999</v>
+        <v>7.436800000000001</v>
       </c>
       <c r="I56" s="5">
         <f>G56*H56</f>
@@ -3764,13 +3764,13 @@
         <v/>
       </c>
       <c r="K56" s="5" t="n">
-        <v>88.23</v>
+        <v>7.2626</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>88.23</v>
+        <v>6.4487</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>88.23</v>
+        <v>6.711666666666666</v>
       </c>
       <c r="N56" s="6">
         <f>J56/M56-1</f>
@@ -3782,24 +3782,24 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>631071</v>
+        <v>583441</v>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>7896007549252</t>
+          <t>7896512944436</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES TRIPLA HIPER M 92UN</t>
+          <t>GRANADO BEBE CR HID 120ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>86.56999999999999</v>
+        <v>21.32</v>
       </c>
       <c r="I57" s="5">
         <f>G57*H57</f>
@@ -3823,13 +3823,13 @@
         <v/>
       </c>
       <c r="K57" s="5" t="n">
-        <v>80.73</v>
+        <v>21.65</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>80.73</v>
+        <v>21.65</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>80.73</v>
+        <v>21.65</v>
       </c>
       <c r="N57" s="6">
         <f>J57/M57-1</f>
@@ -3841,37 +3841,37 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.2% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>631091</v>
+        <v>626251</v>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>7896007551293</t>
+          <t>070942005142</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES TRIPLA HIPER XXG 66</t>
+          <t>GUM ESC DENTAL MIRACULOUS MANUAL 2UN</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>86.56999999999999</v>
+        <v>14.2176</v>
       </c>
       <c r="I58" s="5">
         <f>G58*H58</f>
@@ -3882,13 +3882,13 @@
         <v/>
       </c>
       <c r="K58" s="5" t="n">
-        <v>80.73</v>
+        <v>15.265</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>80.73</v>
+        <v>15.265</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>80.73</v>
+        <v>15.265</v>
       </c>
       <c r="N58" s="6">
         <f>J58/M58-1</f>
@@ -3900,37 +3900,37 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.2% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>556001</v>
+        <v>554541</v>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>7896007549696</t>
+          <t>7908134200040</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>FRALDA SHORTINHO HUGGIES SUPREME CARE XG 24UN</t>
+          <t>GYNOTRAN 750+200MG OVULO 1 STRIP X 7+14 DEDEIRAS</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>51.34</v>
+        <v>87.41460000000001</v>
       </c>
       <c r="I59" s="5">
         <f>G59*H59</f>
@@ -3941,13 +3941,13 @@
         <v/>
       </c>
       <c r="K59" s="5" t="n">
-        <v>47.7</v>
+        <v>90.84</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>44.7033</v>
+        <v>84.2</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>46.7011</v>
+        <v>88.62666666666667</v>
       </c>
       <c r="N59" s="6">
         <f>J59/M59-1</f>
@@ -3959,41 +3959,37 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.6% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (6 un)</t>
-        </is>
-      </c>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>556021</v>
+        <v>648351</v>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>7896007549702</t>
+          <t>7898108640623</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>FRALDA SHORTINHO HUGGIES SUPREME CARE XXG 24UN</t>
+          <t>HASTES FLEX SANCARE 75UN</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>51.34</v>
+        <v>1.767</v>
       </c>
       <c r="I60" s="5">
         <f>G60*H60</f>
@@ -4004,13 +4000,13 @@
         <v/>
       </c>
       <c r="K60" s="5" t="n">
-        <v>50.0233</v>
+        <v>1.8442</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>50.0233</v>
+        <v>1.8442</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>50.0233</v>
+        <v>1.8442</v>
       </c>
       <c r="N60" s="6">
         <f>J60/M60-1</f>
@@ -4022,24 +4018,24 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>594871</v>
+        <v>598351</v>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>7896007548408</t>
+          <t>7896512944443</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>FRD HUG SUPR CARE MEG M 40UN</t>
+          <t>HID INF GRANADO BEBE 120ML LAVANDA</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -4052,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>56.4</v>
+        <v>21.32</v>
       </c>
       <c r="I61" s="5">
         <f>G61*H61</f>
@@ -4063,13 +4059,13 @@
         <v/>
       </c>
       <c r="K61" s="5" t="n">
-        <v>51.9075</v>
+        <v>21.65</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>51.9075</v>
+        <v>21.65</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>51.9075</v>
+        <v>21.65</v>
       </c>
       <c r="N61" s="6">
         <f>J61/M61-1</f>
@@ -4081,37 +4077,37 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +8.7% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>670571</v>
+        <v>284521</v>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>7898216368037</t>
+          <t>7891058002657</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>GARDENAL 100MG C/20 COMP (C1)-REFERENCIA</t>
+          <t>HIDROCLOROTIAZIDA 25MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>9.468</v>
+        <v>2.434242</v>
       </c>
       <c r="I62" s="5">
         <f>G62*H62</f>
@@ -4122,13 +4118,13 @@
         <v/>
       </c>
       <c r="K62" s="5" t="n">
-        <v>9.4094</v>
+        <v>2.38</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>9.4094</v>
+        <v>0.8065</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>9.4094</v>
+        <v>1.8555</v>
       </c>
       <c r="N62" s="6">
         <f>J62/M62-1</f>
@@ -4140,37 +4136,37 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +2.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>630831</v>
+        <v>406241</v>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>7899706178129</t>
+          <t>7897411601505</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>GARNIER AGUA MICELAR 400ML TUDO EM 1</t>
+          <t>HIRUDOID 3MG/G GEL BG X 40G</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>45.67</v>
+        <v>32.016</v>
       </c>
       <c r="I63" s="5">
         <f>G63*H63</f>
@@ -4181,13 +4177,13 @@
         <v/>
       </c>
       <c r="K63" s="5" t="n">
-        <v>44.69</v>
+        <v>32.92</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>44.69</v>
+        <v>28.79</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>44.69</v>
+        <v>31.54333333333333</v>
       </c>
       <c r="N63" s="6">
         <f>J63/M63-1</f>
@@ -4199,37 +4195,37 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.2% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>189141</v>
+        <v>406261</v>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>7891106003230</t>
+          <t>7897411601567</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>GINO CANESTEN 20 MG/G CREME VAG BG 20G+3APLIC</t>
+          <t>HIRUDOID 5MG/G POM BG X 40G</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>73.19619999999999</v>
+        <v>35.0592</v>
       </c>
       <c r="I64" s="5">
         <f>G64*H64</f>
@@ -4240,13 +4236,13 @@
         <v/>
       </c>
       <c r="K64" s="5" t="n">
-        <v>70.93000000000001</v>
+        <v>36.05</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>65.23</v>
+        <v>31.52</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>67.52166666666666</v>
+        <v>34.415</v>
       </c>
       <c r="N64" s="6">
         <f>J64/M64-1</f>
@@ -4258,37 +4254,37 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.2% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>533121</v>
+        <v>646171</v>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>7891721201806</t>
+          <t>7899941202269</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>GLIFAGE XR 500MG CX 30 COMP</t>
+          <t>HORUS MAX TITANIUM FRUTAS VERMELHAS POTE 150G</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>7.436800000000001</v>
+        <v>38.09</v>
       </c>
       <c r="I65" s="5">
         <f>G65*H65</f>
@@ -4299,13 +4295,13 @@
         <v/>
       </c>
       <c r="K65" s="5" t="n">
-        <v>7.2626</v>
+        <v>59.9</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>6.4487</v>
+        <v>59.9</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>6.711666666666666</v>
+        <v>59.9</v>
       </c>
       <c r="N65" s="6">
         <f>J65/M65-1</f>
@@ -4317,37 +4313,37 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.4% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>583441</v>
+        <v>637531</v>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>7896512944436</t>
+          <t>7897211100192</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>GRANADO BEBE CR HID 120ML TRADICIONAL</t>
+          <t>K-Y GEL LUBRIF INTIMO 50G</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>21.32</v>
+        <v>19.3</v>
       </c>
       <c r="I66" s="5">
         <f>G66*H66</f>
@@ -4358,13 +4354,13 @@
         <v/>
       </c>
       <c r="K66" s="5" t="n">
-        <v>21.65</v>
+        <v>18.53</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>21.65</v>
+        <v>18.53</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>21.65</v>
+        <v>18.53</v>
       </c>
       <c r="N66" s="6">
         <f>J66/M66-1</f>
@@ -4376,24 +4372,24 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +4.2% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>626251</v>
+        <v>400901</v>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>070942005142</t>
+          <t>7896641804397</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>GUM ESC DENTAL MIRACULOUS MANUAL 2UN</t>
+          <t>KALOBA 825MG/ML SOL ORAL FR 50ML</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -4406,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>14.2176</v>
+        <v>124.8096</v>
       </c>
       <c r="I67" s="5">
         <f>G67*H67</f>
@@ -4417,13 +4413,13 @@
         <v/>
       </c>
       <c r="K67" s="5" t="n">
-        <v>15.265</v>
+        <v>128.35</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>15.265</v>
+        <v>111.97</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>15.265</v>
+        <v>121.54</v>
       </c>
       <c r="N67" s="6">
         <f>J67/M67-1</f>
@@ -4435,37 +4431,37 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>554541</v>
+        <v>677701</v>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>7908134200040</t>
+          <t>7891150103801</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>GYNOTRAN 750+200MG OVULO 1 STRIP X 7+14 DEDEIRAS</t>
+          <t>KIT SH+COND DOVE HIDRAT+HIA 350ML+175ML</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>87.41460000000001</v>
+        <v>21.52</v>
       </c>
       <c r="I68" s="5">
         <f>G68*H68</f>
@@ -4476,13 +4472,13 @@
         <v/>
       </c>
       <c r="K68" s="5" t="n">
-        <v>90.84</v>
+        <v>28.36</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>84.2</v>
+        <v>28.36</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>88.62666666666667</v>
+        <v>28.36</v>
       </c>
       <c r="N68" s="6">
         <f>J68/M68-1</f>
@@ -4501,17 +4497,17 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>648351</v>
+        <v>22803</v>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>7898108640623</t>
+          <t>4006000101354</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>HASTES FLEX SANCARE 75UN</t>
+          <t>LABIAL NIVEA HIDRACOLOR VERMEL FPS30 4,8G</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
@@ -4524,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>1.767</v>
+        <v>23.3</v>
       </c>
       <c r="I69" s="5">
         <f>G69*H69</f>
@@ -4535,13 +4531,13 @@
         <v/>
       </c>
       <c r="K69" s="5" t="n">
-        <v>1.8442</v>
+        <v>23.18</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>1.8442</v>
+        <v>23.18</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>1.8442</v>
+        <v>23.18</v>
       </c>
       <c r="N69" s="6">
         <f>J69/M69-1</f>
@@ -4553,24 +4549,24 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>598351</v>
+        <v>310061</v>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>7896512944443</t>
+          <t>7897411610750</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>HID INF GRANADO BEBE 120ML LAVANDA</t>
+          <t>LACTULONA 667MG/ML XPE FR 120ML SB AMEIXA</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -4583,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>21.32</v>
+        <v>46.8384</v>
       </c>
       <c r="I70" s="5">
         <f>G70*H70</f>
@@ -4594,13 +4590,13 @@
         <v/>
       </c>
       <c r="K70" s="5" t="n">
-        <v>21.65</v>
+        <v>48.17</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>21.65</v>
+        <v>42.12</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>21.65</v>
+        <v>45.98166666666666</v>
       </c>
       <c r="N70" s="6">
         <f>J70/M70-1</f>
@@ -4612,37 +4608,37 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>284521</v>
+        <v>984</v>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>7891058002657</t>
+          <t>7897947621077</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 25MG CX 30 COMP</t>
+          <t>LAVITAN COMPLEXO B COMP REV FR X 100</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>2.434242</v>
+        <v>38.97</v>
       </c>
       <c r="I71" s="5">
         <f>G71*H71</f>
@@ -4652,56 +4648,44 @@
         <f>H71/E71</f>
         <v/>
       </c>
-      <c r="K71" s="5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>0.8065</v>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v>1.8555</v>
-      </c>
-      <c r="N71" s="6">
-        <f>J71/M71-1</f>
-        <v/>
-      </c>
-      <c r="O71" s="6">
-        <f>J71/K71-1</f>
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="6" t="n"/>
+      <c r="O71" s="6" t="n"/>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.3% (aceito, lim 5%)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>406241</v>
+        <v>564641</v>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>7897411601505</t>
+          <t>7897947601147</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 3MG/G GEL BG X 40G</t>
+          <t>LAVITAN MELATONINA 0,21MG CP PT 90 MOR</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>32.016</v>
+        <v>19.18</v>
       </c>
       <c r="I72" s="5">
         <f>G72*H72</f>
@@ -4712,13 +4696,13 @@
         <v/>
       </c>
       <c r="K72" s="5" t="n">
-        <v>32.92</v>
+        <v>21.94</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>28.79</v>
+        <v>19.59</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>31.54333333333333</v>
+        <v>21.15666666666667</v>
       </c>
       <c r="N72" s="6">
         <f>J72/M72-1</f>
@@ -4737,30 +4721,30 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>406261</v>
+        <v>616351</v>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>7897411601567</t>
+          <t>7897947612594</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 5MG/G POM BG X 40G</t>
+          <t>LAVITAN VIT AZ MULHER COMP REV FR C/ 90</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>35.0592</v>
+        <v>22.22</v>
       </c>
       <c r="I73" s="5">
         <f>G73*H73</f>
@@ -4771,13 +4755,13 @@
         <v/>
       </c>
       <c r="K73" s="5" t="n">
-        <v>36.05</v>
+        <v>21.39</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>31.52</v>
+        <v>21.39</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>34.415</v>
+        <v>21.39</v>
       </c>
       <c r="N73" s="6">
         <f>J73/M73-1</f>
@@ -4789,37 +4773,37 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.9% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>646171</v>
+        <v>646341</v>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>7899941202269</t>
+          <t>7908615053097</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>HORUS MAX TITANIUM FRUTAS VERMELHAS POTE 150G</t>
+          <t>LEAVE IN ELSEVE 100ML CICATRI RENOV BNGA</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>38.09</v>
+        <v>26.54</v>
       </c>
       <c r="I74" s="5">
         <f>G74*H74</f>
@@ -4830,13 +4814,13 @@
         <v/>
       </c>
       <c r="K74" s="5" t="n">
-        <v>59.9</v>
+        <v>30.07</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>59.9</v>
+        <v>30.07</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>59.9</v>
+        <v>30.07</v>
       </c>
       <c r="N74" s="6">
         <f>J74/M74-1</f>
@@ -4848,37 +4832,37 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>637531</v>
+        <v>640591</v>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>7897211100192</t>
+          <t>7898040322540</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>K-Y GEL LUBRIF INTIMO 50G</t>
+          <t>MARESIS (N.S.) SOL SPRAY FR 100ML</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>19.3</v>
+        <v>37.7427</v>
       </c>
       <c r="I75" s="5">
         <f>G75*H75</f>
@@ -4889,13 +4873,13 @@
         <v/>
       </c>
       <c r="K75" s="5" t="n">
-        <v>18.53</v>
+        <v>41.6</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>18.53</v>
+        <v>37.585</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>18.53</v>
+        <v>40.26166666666666</v>
       </c>
       <c r="N75" s="6">
         <f>J75/M75-1</f>
@@ -4907,37 +4891,37 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.2% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>400901</v>
+        <v>665751</v>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>7896641804397</t>
+          <t>7896148500600</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>KALOBA 825MG/ML SOL ORAL FR 50ML</t>
+          <t>MEL DE ABELHA 200G BISNAGA FITOBEL</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>124.8096</v>
+        <v>10.54</v>
       </c>
       <c r="I76" s="5">
         <f>G76*H76</f>
@@ -4948,13 +4932,13 @@
         <v/>
       </c>
       <c r="K76" s="5" t="n">
-        <v>128.35</v>
+        <v>10.54</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>111.97</v>
+        <v>9.43</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>121.54</v>
+        <v>10.17</v>
       </c>
       <c r="N76" s="6">
         <f>J76/M76-1</f>
@@ -4973,30 +4957,30 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>677701</v>
+        <v>345701</v>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>7891150103801</t>
+          <t>7896014669028</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>KIT SH+COND DOVE HIDRAT+HIA 350ML+175ML</t>
+          <t>METREXATO 2,5MG CX 24 COMP</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>21.52</v>
+        <v>25.110068</v>
       </c>
       <c r="I77" s="5">
         <f>G77*H77</f>
@@ -5007,13 +4991,13 @@
         <v/>
       </c>
       <c r="K77" s="5" t="n">
-        <v>28.36</v>
+        <v>24.8467</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>28.36</v>
+        <v>20.995</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>28.36</v>
+        <v>23.38833333333334</v>
       </c>
       <c r="N77" s="6">
         <f>J77/M77-1</f>
@@ -5025,37 +5009,37 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>663141</v>
+        <v>650421</v>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>7891150101630</t>
+          <t>7891800666090</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>KIT SHP+COND SEDA TOQUE DE SEDA 300ML+190ML   UNIL %DN:10.00</t>
+          <t>MICROPOROSA CREMER BRANCA 2,5CMX90CM</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>14.8</v>
+        <v>3.9382</v>
       </c>
       <c r="I78" s="5">
         <f>G78*H78</f>
@@ -5066,13 +5050,13 @@
         <v/>
       </c>
       <c r="K78" s="5" t="n">
-        <v>13.625</v>
+        <v>4.0517</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>13.625</v>
+        <v>3.83</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>13.625</v>
+        <v>3.9778</v>
       </c>
       <c r="N78" s="6">
         <f>J78/M78-1</f>
@@ -5084,37 +5068,37 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +8.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>22803</v>
+        <v>229001</v>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>4006000101354</t>
+          <t>7896212429738</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>LABIAL NIVEA HIDRACOLOR VERMEL FPS30 4,8G</t>
+          <t>MOTILIUM 10MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>23.3</v>
+        <v>27.88</v>
       </c>
       <c r="I79" s="5">
         <f>G79*H79</f>
@@ -5125,13 +5109,13 @@
         <v/>
       </c>
       <c r="K79" s="5" t="n">
-        <v>23.18</v>
+        <v>28.63</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>23.18</v>
+        <v>27.02</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>23.18</v>
+        <v>27.89666666666666</v>
       </c>
       <c r="N79" s="6">
         <f>J79/M79-1</f>
@@ -5143,24 +5127,28 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.5% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (1 un); preços divergentes entre EANs (usado menor)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>310061</v>
+        <v>661311</v>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>7897411610750</t>
+          <t>0618231034291</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>LACTULONA 667MG/ML XPE FR 120ML SB AMEIXA</t>
+          <t>MULTIVITALE VIT D 2.000UI 60CPS</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -5173,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>46.8384</v>
+        <v>18.31</v>
       </c>
       <c r="I80" s="5">
         <f>G80*H80</f>
@@ -5184,13 +5172,13 @@
         <v/>
       </c>
       <c r="K80" s="5" t="n">
-        <v>48.17</v>
+        <v>18.31</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>42.12</v>
+        <v>18.31</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>45.98166666666666</v>
+        <v>18.31</v>
       </c>
       <c r="N80" s="6">
         <f>J80/M80-1</f>
@@ -5209,17 +5197,17 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>984</v>
+        <v>651901</v>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>7897947621077</t>
+          <t>7898108640050</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN COMPLEXO B COMP REV FR X 100</t>
+          <t>N COMPRESSA GAZES 11FIOS ESTER 5UND   SANF %DN:0.00</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -5232,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>38.97</v>
+        <v>0.8929999999999999</v>
       </c>
       <c r="I81" s="5">
         <f>G81*H81</f>
@@ -5242,44 +5230,56 @@
         <f>H81/E81</f>
         <v/>
       </c>
-      <c r="K81" s="5" t="n"/>
-      <c r="L81" s="5" t="n"/>
-      <c r="M81" s="5" t="n"/>
-      <c r="N81" s="6" t="n"/>
-      <c r="O81" s="6" t="n"/>
+      <c r="K81" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N81" s="6">
+        <f>J81/M81-1</f>
+        <v/>
+      </c>
+      <c r="O81" s="6">
+        <f>J81/K81-1</f>
+        <v/>
+      </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>564641</v>
+        <v>669941</v>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>7897947601147</t>
+          <t>7506306255678</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN MELATONINA 0,21MG CP PT 90 MOR</t>
+          <t>N SAB DOVE ESFOLIANTE BEAUTY SCRUB COCO 280G   UNIL %DN:0.00</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>19.18</v>
+        <v>38.79</v>
       </c>
       <c r="I82" s="5">
         <f>G82*H82</f>
@@ -5290,13 +5290,13 @@
         <v/>
       </c>
       <c r="K82" s="5" t="n">
-        <v>21.94</v>
+        <v>37.43</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>19.59</v>
+        <v>37.43</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>21.15666666666667</v>
+        <v>37.43</v>
       </c>
       <c r="N82" s="6">
         <f>J82/M82-1</f>
@@ -5308,37 +5308,37 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +3.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>546241</v>
+        <v>556401</v>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>7897947616509</t>
+          <t>7896677704890</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN MULTI HOMEM 5G 60CP</t>
+          <t>NERVOCALM 250MG CX 20 COMP</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>39.92</v>
+        <v>30.15</v>
       </c>
       <c r="I83" s="5">
         <f>G83*H83</f>
@@ -5349,13 +5349,13 @@
         <v/>
       </c>
       <c r="K83" s="5" t="n">
-        <v>36.5</v>
+        <v>31.33</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>32.59</v>
+        <v>22.32</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>35.19666666666667</v>
+        <v>28.32666666666666</v>
       </c>
       <c r="N83" s="6">
         <f>J83/M83-1</f>
@@ -5367,37 +5367,37 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +9.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>546261</v>
+        <v>358321</v>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>7897947616516</t>
+          <t>7894916500333</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN MULTI MULHER 5G 60CP</t>
+          <t>NEUTROFER 300MG FR 30 COMP</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>39.92</v>
+        <v>47.21925</v>
       </c>
       <c r="I84" s="5">
         <f>G84*H84</f>
@@ -5408,13 +5408,13 @@
         <v/>
       </c>
       <c r="K84" s="5" t="n">
-        <v>38.33</v>
+        <v>45.04</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>32.59</v>
+        <v>44.905</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>36.41666666666666</v>
+        <v>44.995</v>
       </c>
       <c r="N84" s="6">
         <f>J84/M84-1</f>
@@ -5426,37 +5426,37 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.1% (aceito, lim 5%)</t>
+          <t>REAJUSTE +4.9% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>616351</v>
+        <v>443</v>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>7897947612594</t>
+          <t>7891010704490</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN VIT AZ MULHER COMP REV FR C/ 90</t>
+          <t>NEUTROG D CLEAN ESF ENER 100G</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>22.22</v>
+        <v>33.46</v>
       </c>
       <c r="I85" s="5">
         <f>G85*H85</f>
@@ -5467,13 +5467,13 @@
         <v/>
       </c>
       <c r="K85" s="5" t="n">
-        <v>21.39</v>
+        <v>33.105</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>21.39</v>
+        <v>33.105</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>21.39</v>
+        <v>33.105</v>
       </c>
       <c r="N85" s="6">
         <f>J85/M85-1</f>
@@ -5485,37 +5485,37 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.9% (aceito, lim 5%)</t>
+          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>646341</v>
+        <v>563181</v>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>7908615053097</t>
+          <t>7896523224435</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>LEAVE IN ELSEVE 100ML CICATRI RENOV BNGA</t>
+          <t>OLEO MINERAL FR 100 ML</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>26.54</v>
+        <v>7.2</v>
       </c>
       <c r="I86" s="5">
         <f>G86*H86</f>
@@ -5526,13 +5526,13 @@
         <v/>
       </c>
       <c r="K86" s="5" t="n">
-        <v>30.07</v>
+        <v>6.99</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>30.07</v>
+        <v>6.99</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>30.07</v>
+        <v>6.989999999999999</v>
       </c>
       <c r="N86" s="6">
         <f>J86/M86-1</f>
@@ -5544,24 +5544,24 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>640591</v>
+        <v>609511</v>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>7898040322540</t>
+          <t>7897316806388</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>MARESIS (N.S.) SOL SPRAY FR 100ML</t>
+          <t>OPTIVE FR 15ML</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -5574,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>37.7427</v>
+        <v>65.136</v>
       </c>
       <c r="I87" s="5">
         <f>G87*H87</f>
@@ -5585,13 +5585,13 @@
         <v/>
       </c>
       <c r="K87" s="5" t="n">
-        <v>41.6</v>
+        <v>81.22</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>37.585</v>
+        <v>73.28</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>40.26166666666666</v>
+        <v>78.57333333333334</v>
       </c>
       <c r="N87" s="6">
         <f>J87/M87-1</f>
@@ -5610,17 +5610,17 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>665751</v>
+        <v>630971</v>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>7896148500600</t>
+          <t>7896902209749</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>MEL DE ABELHA 200G BISNAGA FITOBEL</t>
+          <t>PEDRA HUME FARMAX 30ML C/GLIC SPRAY</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -5633,7 +5633,7 @@
         <v>2</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>10.54</v>
+        <v>7.04</v>
       </c>
       <c r="I88" s="5">
         <f>G88*H88</f>
@@ -5644,13 +5644,13 @@
         <v/>
       </c>
       <c r="K88" s="5" t="n">
-        <v>10.54</v>
+        <v>7.04</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>9.43</v>
+        <v>7.04</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>10.17</v>
+        <v>7.04</v>
       </c>
       <c r="N88" s="6">
         <f>J88/M88-1</f>
@@ -5669,30 +5669,30 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>345701</v>
+        <v>319641</v>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>7896014669028</t>
+          <t>7891058003562</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>METREXATO 2,5MG CX 24 COMP</t>
+          <t>PURAN T4 37,5MCG CX 30 COMP</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>25.110068</v>
+        <v>8.487500000000001</v>
       </c>
       <c r="I89" s="5">
         <f>G89*H89</f>
@@ -5703,13 +5703,13 @@
         <v/>
       </c>
       <c r="K89" s="5" t="n">
-        <v>24.8467</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>20.995</v>
+        <v>7.6</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>23.38833333333334</v>
+        <v>7.988333333333334</v>
       </c>
       <c r="N89" s="6">
         <f>J89/M89-1</f>
@@ -5721,37 +5721,37 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +2.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>650421</v>
+        <v>604551</v>
       </c>
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>7891800666090</t>
+          <t>7891010253691</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>MICROPOROSA CREMER BRANCA 2,5CMX90CM</t>
+          <t>PV - SAB.LIQ.JOHN.K.200ML LIMP.S.PO</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>3.9382</v>
+        <v>19.5</v>
       </c>
       <c r="I90" s="5">
         <f>G90*H90</f>
@@ -5762,13 +5762,13 @@
         <v/>
       </c>
       <c r="K90" s="5" t="n">
-        <v>4.0517</v>
+        <v>19.5333</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>3.83</v>
+        <v>19.5333</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>3.9778</v>
+        <v>19.5333</v>
       </c>
       <c r="N90" s="6">
         <f>J90/M90-1</f>
@@ -5783,34 +5783,38 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (1 un)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>229001</v>
+        <v>662901</v>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>7896212429738</t>
+          <t>7897947619548</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>MOTILIUM 10MG CX 30 COMP</t>
+          <t>PVV - LAVITAN OMEGA COMPLEX CAP GEL PT X 30 SF</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>27.88</v>
+        <v>50.46</v>
       </c>
       <c r="I91" s="5">
         <f>G91*H91</f>
@@ -5820,60 +5824,44 @@
         <f>H91/E91</f>
         <v/>
       </c>
-      <c r="K91" s="5" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>27.02</v>
-      </c>
-      <c r="M91" s="5" t="n">
-        <v>27.89666666666666</v>
-      </c>
-      <c r="N91" s="6">
-        <f>J91/M91-1</f>
-        <v/>
-      </c>
-      <c r="O91" s="6">
-        <f>J91/K91-1</f>
-        <v/>
-      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="6" t="n"/>
+      <c r="O91" s="6" t="n"/>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un); preços divergentes entre EANs (usado menor)</t>
-        </is>
-      </c>
+          <t>SEM HISTÓRICO</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>661311</v>
+        <v>598361</v>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>0618231034291</t>
+          <t>7896902201255</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>MULTIVITALE VIT D 2.000UI 60CPS</t>
+          <t>REMOV ESM FARMAX 100ML S/ACET VITAM</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>18.31</v>
+        <v>3.79</v>
       </c>
       <c r="I92" s="5">
         <f>G92*H92</f>
@@ -5884,13 +5872,13 @@
         <v/>
       </c>
       <c r="K92" s="5" t="n">
-        <v>18.31</v>
+        <v>4.56</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>18.31</v>
+        <v>4.56</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>18.31</v>
+        <v>4.56</v>
       </c>
       <c r="N92" s="6">
         <f>J92/M92-1</f>
@@ -5902,37 +5890,37 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>651901</v>
+        <v>607761</v>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>7898108640050</t>
+          <t>7894650009567</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>N COMPRESSA GAZES 11FIOS ESTER 5UND   SANF %DN:0.00</t>
+          <t>REP OFF FAMILY SPRAY 170ML</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.8929999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="I93" s="5">
         <f>G93*H93</f>
@@ -5943,13 +5931,13 @@
         <v/>
       </c>
       <c r="K93" s="5" t="n">
-        <v>0.92</v>
+        <v>18.38</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.92</v>
+        <v>18.38</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0.92</v>
+        <v>18.38</v>
       </c>
       <c r="N93" s="6">
         <f>J93/M93-1</f>
@@ -5961,37 +5949,37 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>669941</v>
+        <v>544781</v>
       </c>
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>7506306255678</t>
+          <t>7894650005712</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>N SAB DOVE ESFOLIANTE BEAUTY SCRUB COCO 280G   UNIL %DN:0.00</t>
+          <t>REP OFF KIDS LOCAO 117ML</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>38.79</v>
+        <v>19.84</v>
       </c>
       <c r="I94" s="5">
         <f>G94*H94</f>
@@ -6002,13 +5990,13 @@
         <v/>
       </c>
       <c r="K94" s="5" t="n">
-        <v>37.43</v>
+        <v>20.92</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>37.43</v>
+        <v>20.92</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>37.43</v>
+        <v>20.92</v>
       </c>
       <c r="N94" s="6">
         <f>J94/M94-1</f>
@@ -6020,37 +6008,37 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>556401</v>
+        <v>623921</v>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>7896677704890</t>
+          <t>7509546678832</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>NERVOCALM 250MG CX 20 COMP</t>
+          <t>SAB BARRA PROTEX CARVAO 85G</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>30.15</v>
+        <v>3.55</v>
       </c>
       <c r="I95" s="5">
         <f>G95*H95</f>
@@ -6061,13 +6049,13 @@
         <v/>
       </c>
       <c r="K95" s="5" t="n">
-        <v>31.33</v>
+        <v>3.75</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>22.32</v>
+        <v>3.75</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>28.32666666666666</v>
+        <v>3.75</v>
       </c>
       <c r="N95" s="6">
         <f>J95/M95-1</f>
@@ -6086,30 +6074,30 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>358321</v>
+        <v>843</v>
       </c>
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>7894916500333</t>
+          <t>7891010781668</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>NEUTROFER 300MG FR 30 COMP</t>
+          <t>SAB J J BABY HORA DO SONO 80G</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>47.21925</v>
+        <v>5.63</v>
       </c>
       <c r="I96" s="5">
         <f>G96*H96</f>
@@ -6120,13 +6108,13 @@
         <v/>
       </c>
       <c r="K96" s="5" t="n">
-        <v>45.04</v>
+        <v>5.79</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>44.905</v>
+        <v>5.79</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>44.995</v>
+        <v>5.79</v>
       </c>
       <c r="N96" s="6">
         <f>J96/M96-1</f>
@@ -6138,37 +6126,37 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>443</v>
+        <v>571261</v>
       </c>
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>7891010704490</t>
+          <t>7891024027257</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>NEUTROG D CLEAN ESF ENER 100G</t>
+          <t>SAB LIQ PROTEX 200ML REF VIT E</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>33.46</v>
+        <v>7.75</v>
       </c>
       <c r="I97" s="5">
         <f>G97*H97</f>
@@ -6179,13 +6167,13 @@
         <v/>
       </c>
       <c r="K97" s="5" t="n">
-        <v>33.105</v>
+        <v>7.59</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>33.105</v>
+        <v>7.31</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>33.105</v>
+        <v>7.496666666666666</v>
       </c>
       <c r="N97" s="6">
         <f>J97/M97-1</f>
@@ -6197,37 +6185,37 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +2.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>563181</v>
+        <v>623971</v>
       </c>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>7896523224435</t>
+          <t>7509546665986</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>OLEO MINERAL FR 100 ML</t>
+          <t>SAB LIQ PROTEX PUM ERVA DOCE 400ML</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>7.2</v>
+        <v>16.67</v>
       </c>
       <c r="I98" s="5">
         <f>G98*H98</f>
@@ -6238,13 +6226,13 @@
         <v/>
       </c>
       <c r="K98" s="5" t="n">
-        <v>6.99</v>
+        <v>19.53</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>6.99</v>
+        <v>19.53</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>6.989999999999999</v>
+        <v>19.53</v>
       </c>
       <c r="N98" s="6">
         <f>J98/M98-1</f>
@@ -6256,37 +6244,37 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.0% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>609511</v>
+        <v>689301</v>
       </c>
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>7897316806388</t>
+          <t>7891150083042</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>OPTIVE FR 15ML</t>
+          <t>SAB LIQ REXONA ANTIBAC FRESH 250ML</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>65.136</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I99" s="5">
         <f>G99*H99</f>
@@ -6297,13 +6285,13 @@
         <v/>
       </c>
       <c r="K99" s="5" t="n">
-        <v>81.22</v>
+        <v>9.58</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>73.28</v>
+        <v>9.58</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>78.57333333333334</v>
+        <v>9.58</v>
       </c>
       <c r="N99" s="6">
         <f>J99/M99-1</f>
@@ -6315,37 +6303,37 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>630971</v>
+        <v>598481</v>
       </c>
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>7896902209749</t>
+          <t>7891024035313</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>PEDRA HUME FARMAX 30ML C/GLIC SPRAY</t>
+          <t>SAB PROTEX MEN SPORT 85G</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>7.04</v>
+        <v>3.55</v>
       </c>
       <c r="I100" s="5">
         <f>G100*H100</f>
@@ -6356,13 +6344,13 @@
         <v/>
       </c>
       <c r="K100" s="5" t="n">
-        <v>7.04</v>
+        <v>35.535</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>7.04</v>
+        <v>35.535</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>7.04</v>
+        <v>35.535</v>
       </c>
       <c r="N100" s="6">
         <f>J100/M100-1</f>
@@ -6374,37 +6362,41 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>conferir emb.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>563761</v>
+        <v>545341</v>
       </c>
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>7891035991110</t>
+          <t>7896018700789</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>PRES JONTEX ULTRA SENSITIVE C2UN</t>
+          <t>SABONETE INFANTIL BARRA CHÁ DE CAMOMILA DISNEY BABY HUGGIES 75G</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>13.1908</v>
+        <v>4.55</v>
       </c>
       <c r="I101" s="5">
         <f>G101*H101</f>
@@ -6415,13 +6407,13 @@
         <v/>
       </c>
       <c r="K101" s="5" t="n">
-        <v>12.06</v>
+        <v>4.55</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>11.4783</v>
+        <v>4.55</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>11.4783</v>
+        <v>4.55</v>
       </c>
       <c r="N101" s="6">
         <f>J101/M101-1</f>
@@ -6433,37 +6425,37 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +9.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>658711</v>
+        <v>672851</v>
       </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>609963220755</t>
+          <t>7891150097643</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>PRINCIPIA GEL LIMPEZA FAC GL-02 350G</t>
+          <t>SH DOVE BOND 350ML+COND 150ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>41.26</v>
+        <v>21.52</v>
       </c>
       <c r="I102" s="5">
         <f>G102*H102</f>
@@ -6474,13 +6466,13 @@
         <v/>
       </c>
       <c r="K102" s="5" t="n">
-        <v>38.64</v>
+        <v>32.18</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>34.3</v>
+        <v>32.18</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>37.19333333333334</v>
+        <v>32.18</v>
       </c>
       <c r="N102" s="6">
         <f>J102/M102-1</f>
@@ -6492,37 +6484,37 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.8% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>319641</v>
+        <v>672151</v>
       </c>
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>7891058003562</t>
+          <t>7908966528404</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 37,5MCG CX 30 COMP</t>
+          <t>SH ELSEVE COLAGENO 200ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>8.487500000000001</v>
+        <v>14.37</v>
       </c>
       <c r="I103" s="5">
         <f>G103*H103</f>
@@ -6533,13 +6525,13 @@
         <v/>
       </c>
       <c r="K103" s="5" t="n">
-        <v>8.255000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>7.6</v>
+        <v>12.96</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>7.988333333333334</v>
+        <v>12.96</v>
       </c>
       <c r="N103" s="6">
         <f>J103/M103-1</f>
@@ -6551,37 +6543,37 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>604551</v>
+        <v>635261</v>
       </c>
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>7891010253691</t>
+          <t>7891033535026</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>PV - SAB.LIQ.JOHN.K.200ML LIMP.S.PO</t>
+          <t>SIAGE SH ACELERA CRESCIMENTO 250ML</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>19.5</v>
+        <v>40.7</v>
       </c>
       <c r="I104" s="5">
         <f>G104*H104</f>
@@ -6592,13 +6584,13 @@
         <v/>
       </c>
       <c r="K104" s="5" t="n">
-        <v>19.5333</v>
+        <v>42.58</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>19.5333</v>
+        <v>42.58</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>19.5333</v>
+        <v>42.58</v>
       </c>
       <c r="N104" s="6">
         <f>J104/M104-1</f>
@@ -6610,41 +6602,37 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un)</t>
-        </is>
-      </c>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>616811</v>
+        <v>605291</v>
       </c>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>7899852022833</t>
+          <t>7897460401934</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>PV - VULT CARE CREME FAC HID UNIFORMIZAD 100G</t>
+          <t>SILIMALON 100+70MG CX 10 COMP REV</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>23.56</v>
+        <v>18.729</v>
       </c>
       <c r="I105" s="5">
         <f>G105*H105</f>
@@ -6655,13 +6643,13 @@
         <v/>
       </c>
       <c r="K105" s="5" t="n">
-        <v>21.65</v>
+        <v>19.2467</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>21.65</v>
+        <v>15.4333</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>21.65</v>
+        <v>17.66546666666667</v>
       </c>
       <c r="N105" s="6">
         <f>J105/M105-1</f>
@@ -6673,37 +6661,37 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +8.8% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>662901</v>
+        <v>434001</v>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>7897947619548</t>
+          <t>7897460401743</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>PVV - LAVITAN OMEGA COMPLEX CAP GEL PT X 30 SF</t>
+          <t>SILIMALON 140 140+100MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>50.46</v>
+        <v>89.982</v>
       </c>
       <c r="I106" s="5">
         <f>G106*H106</f>
@@ -6713,44 +6701,56 @@
         <f>H106/E106</f>
         <v/>
       </c>
-      <c r="K106" s="5" t="n"/>
-      <c r="L106" s="5" t="n"/>
-      <c r="M106" s="5" t="n"/>
-      <c r="N106" s="6" t="n"/>
-      <c r="O106" s="6" t="n"/>
+      <c r="K106" s="5" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>88.16223333333335</v>
+      </c>
+      <c r="N106" s="6">
+        <f>J106/M106-1</f>
+        <v/>
+      </c>
+      <c r="O106" s="6">
+        <f>J106/K106-1</f>
+        <v/>
+      </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>598361</v>
+        <v>529941</v>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>7896902201255</t>
+          <t>7908134200552</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>REMOV ESM FARMAX 100ML S/ACET VITAM</t>
+          <t>SLINDA 4MG (CAIXA C/ 3 CARTELAS) C/28 COMP REV</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>3.79</v>
+        <v>219.2827</v>
       </c>
       <c r="I107" s="5">
         <f>G107*H107</f>
@@ -6761,13 +6761,13 @@
         <v/>
       </c>
       <c r="K107" s="5" t="n">
-        <v>4.56</v>
+        <v>226.51</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>4.56</v>
+        <v>67.41330000000001</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>4.56</v>
+        <v>121.7522</v>
       </c>
       <c r="N107" s="6">
         <f>J107/M107-1</f>
@@ -6779,37 +6779,37 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>607761</v>
+        <v>529921</v>
       </c>
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>7894650009567</t>
+          <t>7908134200453</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>REP OFF FAMILY SPRAY 170ML</t>
+          <t>SLINDA 4MG CX 24 COMP REV+4 PLACEBOS</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>17.2</v>
+        <v>92.04650000000001</v>
       </c>
       <c r="I108" s="5">
         <f>G108*H108</f>
@@ -6820,13 +6820,13 @@
         <v/>
       </c>
       <c r="K108" s="5" t="n">
-        <v>18.38</v>
+        <v>95.08</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>18.38</v>
+        <v>89.83499999999999</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>18.38</v>
+        <v>91.58333333333333</v>
       </c>
       <c r="N108" s="6">
         <f>J108/M108-1</f>
@@ -6838,37 +6838,37 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>544781</v>
+        <v>558381</v>
       </c>
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>7894650005712</t>
+          <t>7896902212152</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>REP OFF KIDS LOCAO 117ML</t>
+          <t>SOLUCAO SORIMAX 100 ML</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>19.84</v>
+        <v>2.39</v>
       </c>
       <c r="I109" s="5">
         <f>G109*H109</f>
@@ -6879,13 +6879,13 @@
         <v/>
       </c>
       <c r="K109" s="5" t="n">
-        <v>20.92</v>
+        <v>2.69</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>20.92</v>
+        <v>2.69</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>20.92</v>
+        <v>2.69</v>
       </c>
       <c r="N109" s="6">
         <f>J109/M109-1</f>
@@ -6897,24 +6897,24 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>590241</v>
+        <v>661151</v>
       </c>
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>7894650013380</t>
+          <t>7899852025469</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>REPEL OFF LOCAO BABY 117ML</t>
+          <t>SPR VULT RECARGA HIDRT 100ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -6927,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>27.22</v>
+        <v>27.38</v>
       </c>
       <c r="I110" s="5">
         <f>G110*H110</f>
@@ -6938,13 +6938,13 @@
         <v/>
       </c>
       <c r="K110" s="5" t="n">
-        <v>25.34</v>
+        <v>27.51</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>25.34</v>
+        <v>27.51</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>25.34</v>
+        <v>27.51</v>
       </c>
       <c r="N110" s="6">
         <f>J110/M110-1</f>
@@ -6956,24 +6956,24 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>623921</v>
+        <v>624141</v>
       </c>
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>7509546678832</t>
+          <t>7506339305142</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>SAB BARRA PROTEX CARVAO 85G</t>
+          <t>TESTE GRAV CLEARBLUE PLUS 2UNI-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -6986,7 +6986,7 @@
         <v>2</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>3.55</v>
+        <v>23.84</v>
       </c>
       <c r="I111" s="5">
         <f>G111*H111</f>
@@ -6997,13 +6997,13 @@
         <v/>
       </c>
       <c r="K111" s="5" t="n">
-        <v>3.75</v>
+        <v>24.7675</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>3.75</v>
+        <v>23.11</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>3.75</v>
+        <v>24.215</v>
       </c>
       <c r="N111" s="6">
         <f>J111/M111-1</f>
@@ -7015,37 +7015,37 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>843</v>
+        <v>622921</v>
       </c>
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>7891010781668</t>
+          <t>7500435137959</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>SAB J J BABY HORA DO SONO 80G</t>
+          <t>TESTE GRAV CLEARBLUE SAIBA ANTES-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>5.63</v>
+        <v>18.753</v>
       </c>
       <c r="I112" s="5">
         <f>G112*H112</f>
@@ -7056,13 +7056,13 @@
         <v/>
       </c>
       <c r="K112" s="5" t="n">
-        <v>5.79</v>
+        <v>21.65</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>5.79</v>
+        <v>19.62</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>5.79</v>
+        <v>20.60666666666667</v>
       </c>
       <c r="N112" s="6">
         <f>J112/M112-1</f>
@@ -7074,37 +7074,37 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>571261</v>
+        <v>610651</v>
       </c>
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>7891024027257</t>
+          <t>7908032300866</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ PROTEX 200ML REF VIT E</t>
+          <t>TOALHAS UMED PIQUITUCHO PRATIC C/48UND</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>7.75</v>
+        <v>4.0255</v>
       </c>
       <c r="I113" s="5">
         <f>G113*H113</f>
@@ -7115,13 +7115,13 @@
         <v/>
       </c>
       <c r="K113" s="5" t="n">
-        <v>7.59</v>
+        <v>6.03</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>7.31</v>
+        <v>6.03</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>7.496666666666666</v>
+        <v>6.03</v>
       </c>
       <c r="N113" s="6">
         <f>J113/M113-1</f>
@@ -7133,37 +7133,37 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.1% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>623971</v>
+        <v>319341</v>
       </c>
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>7509546665986</t>
+          <t>7891045008433</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ PROTEX PUM ERVA DOCE 400ML</t>
+          <t>V - NORDETTE 0,15+0,03MG CX 21 DRG</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>16.67</v>
+        <v>9.927499999999998</v>
       </c>
       <c r="I114" s="5">
         <f>G114*H114</f>
@@ -7174,13 +7174,13 @@
         <v/>
       </c>
       <c r="K114" s="5" t="n">
-        <v>19.53</v>
+        <v>10.31</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>19.53</v>
+        <v>9.265000000000001</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>19.53</v>
+        <v>9.831666666666667</v>
       </c>
       <c r="N114" s="6">
         <f>J114/M114-1</f>
@@ -7192,37 +7192,37 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>689301</v>
+        <v>654331</v>
       </c>
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>7891150083042</t>
+          <t>7891653014260</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ REXONA ANTIBAC FRESH 250ML</t>
+          <t>VAGISIL DEO INTIMO JASMIN BRANCO 75ML</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>25.77</v>
       </c>
       <c r="I115" s="5">
         <f>G115*H115</f>
@@ -7233,13 +7233,13 @@
         <v/>
       </c>
       <c r="K115" s="5" t="n">
-        <v>9.58</v>
+        <v>24.47</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>9.58</v>
+        <v>24.47</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>9.58</v>
+        <v>24.47</v>
       </c>
       <c r="N115" s="6">
         <f>J115/M115-1</f>
@@ -7251,37 +7251,37 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>538881</v>
+        <v>662301</v>
       </c>
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>7891150060234</t>
+          <t>7891653014031</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ ROSAS FRANCESAS LUX  200ML REFIL</t>
+          <t>VAGISIL DEO INTIMO ODOR BLOCK 60ML</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>6.4</v>
+        <v>22.43</v>
       </c>
       <c r="I116" s="5">
         <f>G116*H116</f>
@@ -7292,13 +7292,13 @@
         <v/>
       </c>
       <c r="K116" s="5" t="n">
-        <v>5.9558</v>
+        <v>22.43</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>4.4775</v>
+        <v>22.42</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>5.463033333333333</v>
+        <v>22.42666666666667</v>
       </c>
       <c r="N116" s="6">
         <f>J116/M116-1</f>
@@ -7310,37 +7310,37 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.5% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>598481</v>
+        <v>654311</v>
       </c>
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>7891024035313</t>
+          <t>7891653040078</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>SAB PROTEX MEN SPORT 85G</t>
+          <t>VAGISIL SAB INTIMO URIN PROTECT 300ML</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>3.55</v>
+        <v>21.67</v>
       </c>
       <c r="I117" s="5">
         <f>G117*H117</f>
@@ -7351,13 +7351,13 @@
         <v/>
       </c>
       <c r="K117" s="5" t="n">
-        <v>35.535</v>
+        <v>21.68</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>35.535</v>
+        <v>17.95</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>35.535</v>
+        <v>20.43666666666667</v>
       </c>
       <c r="N117" s="6">
         <f>J117/M117-1</f>
@@ -7369,1509 +7369,30 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>conferir emb.</t>
+          <t>estoque parcial (1 un)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>605611</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr"/>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>7898422746827</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>SAB.DOVE 90G ESFOLIACAO DIARIA</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="I118" s="5">
-        <f>G118*H118</f>
-        <v/>
-      </c>
-      <c r="J118" s="5">
-        <f>H118/E118</f>
-        <v/>
-      </c>
-      <c r="K118" s="5" t="n">
-        <v>4.9258</v>
-      </c>
-      <c r="L118" s="5" t="n">
-        <v>4.9258</v>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v>4.9258</v>
-      </c>
-      <c r="N118" s="6">
-        <f>J118/M118-1</f>
-        <v/>
-      </c>
-      <c r="O118" s="6">
-        <f>J118/K118-1</f>
-        <v/>
-      </c>
-      <c r="P118" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +9.8% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>545341</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr"/>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>7896018700789</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>SABONETE INFANTIL BARRA CHÁ DE CAMOMILA DISNEY BABY HUGGIES 75G</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="I119" s="5">
-        <f>G119*H119</f>
-        <v/>
-      </c>
-      <c r="J119" s="5">
-        <f>H119/E119</f>
-        <v/>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="L119" s="5" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="M119" s="5" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="N119" s="6">
-        <f>J119/M119-1</f>
-        <v/>
-      </c>
-      <c r="O119" s="6">
-        <f>J119/K119-1</f>
-        <v/>
-      </c>
-      <c r="P119" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr"/>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I118" s="8">
+        <f>SUM(I2:I117)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>696101</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr"/>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>0609963220359</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>SERUM VIT C 10%+FERULICO VC-10 - ANTIOXIDANTE 30ML</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>57.52</v>
-      </c>
-      <c r="I120" s="5">
-        <f>G120*H120</f>
-        <v/>
-      </c>
-      <c r="J120" s="5">
-        <f>H120/E120</f>
-        <v/>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v>53.39000000000001</v>
-      </c>
-      <c r="N120" s="6">
-        <f>J120/M120-1</f>
-        <v/>
-      </c>
-      <c r="O120" s="6">
-        <f>J120/K120-1</f>
-        <v/>
-      </c>
-      <c r="P120" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +7.7% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>672851</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr"/>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>7891150097643</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>SH DOVE BOND 350ML+COND 150ML-DEMAIS PROD</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G121" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>21.52</v>
-      </c>
-      <c r="I121" s="5">
-        <f>G121*H121</f>
-        <v/>
-      </c>
-      <c r="J121" s="5">
-        <f>H121/E121</f>
-        <v/>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="L121" s="5" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="N121" s="6">
-        <f>J121/M121-1</f>
-        <v/>
-      </c>
-      <c r="O121" s="6">
-        <f>J121/K121-1</f>
-        <v/>
-      </c>
-      <c r="P121" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>672151</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr"/>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>7908966528404</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>SH ELSEVE COLAGENO 200ML-DEMAIS PROD</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G122" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>14.37</v>
-      </c>
-      <c r="I122" s="5">
-        <f>G122*H122</f>
-        <v/>
-      </c>
-      <c r="J122" s="5">
-        <f>H122/E122</f>
-        <v/>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="L122" s="5" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="N122" s="6">
-        <f>J122/M122-1</f>
-        <v/>
-      </c>
-      <c r="O122" s="6">
-        <f>J122/K122-1</f>
-        <v/>
-      </c>
-      <c r="P122" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>635261</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr"/>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>7891033535026</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>SIAGE SH ACELERA CRESCIMENTO 250ML</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="I123" s="5">
-        <f>G123*H123</f>
-        <v/>
-      </c>
-      <c r="J123" s="5">
-        <f>H123/E123</f>
-        <v/>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="L123" s="5" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="N123" s="6">
-        <f>J123/M123-1</f>
-        <v/>
-      </c>
-      <c r="O123" s="6">
-        <f>J123/K123-1</f>
-        <v/>
-      </c>
-      <c r="P123" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>634941</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr"/>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>7891033530946</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>SIAGE SH PRO CRONOLOGY 250ML</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="I124" s="5">
-        <f>G124*H124</f>
-        <v/>
-      </c>
-      <c r="J124" s="5">
-        <f>H124/E124</f>
-        <v/>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>38.32</v>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v>38.32</v>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v>38.32</v>
-      </c>
-      <c r="N124" s="6">
-        <f>J124/M124-1</f>
-        <v/>
-      </c>
-      <c r="O124" s="6">
-        <f>J124/K124-1</f>
-        <v/>
-      </c>
-      <c r="P124" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +6.2% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>605291</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr"/>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>7897460401934</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>SILIMALON 100+70MG CX 10 COMP REV</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G125" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>18.729</v>
-      </c>
-      <c r="I125" s="5">
-        <f>G125*H125</f>
-        <v/>
-      </c>
-      <c r="J125" s="5">
-        <f>H125/E125</f>
-        <v/>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>19.2467</v>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v>15.4333</v>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v>17.66546666666667</v>
-      </c>
-      <c r="N125" s="6">
-        <f>J125/M125-1</f>
-        <v/>
-      </c>
-      <c r="O125" s="6">
-        <f>J125/K125-1</f>
-        <v/>
-      </c>
-      <c r="P125" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>434001</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr"/>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>7897460401743</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>SILIMALON 140 140+100MG CX 30 COMP REV</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>89.982</v>
-      </c>
-      <c r="I126" s="5">
-        <f>G126*H126</f>
-        <v/>
-      </c>
-      <c r="J126" s="5">
-        <f>H126/E126</f>
-        <v/>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>92.47</v>
-      </c>
-      <c r="L126" s="5" t="n">
-        <v>84.03</v>
-      </c>
-      <c r="M126" s="5" t="n">
-        <v>88.16223333333335</v>
-      </c>
-      <c r="N126" s="6">
-        <f>J126/M126-1</f>
-        <v/>
-      </c>
-      <c r="O126" s="6">
-        <f>J126/K126-1</f>
-        <v/>
-      </c>
-      <c r="P126" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>433961</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr"/>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>7897460401750</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>SILIMALON 140 140+100MG CX 60 COMP REV</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>137.556</v>
-      </c>
-      <c r="I127" s="5">
-        <f>G127*H127</f>
-        <v/>
-      </c>
-      <c r="J127" s="5">
-        <f>H127/E127</f>
-        <v/>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>128.47</v>
-      </c>
-      <c r="L127" s="5" t="n">
-        <v>128.47</v>
-      </c>
-      <c r="M127" s="5" t="n">
-        <v>128.47</v>
-      </c>
-      <c r="N127" s="6">
-        <f>J127/M127-1</f>
-        <v/>
-      </c>
-      <c r="O127" s="6">
-        <f>J127/K127-1</f>
-        <v/>
-      </c>
-      <c r="P127" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +7.1% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>529941</v>
-      </c>
-      <c r="B128" s="2" t="inlineStr"/>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>7908134200552</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>SLINDA 4MG (CAIXA C/ 3 CARTELAS) C/28 COMP REV</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G128" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>219.2827</v>
-      </c>
-      <c r="I128" s="5">
-        <f>G128*H128</f>
-        <v/>
-      </c>
-      <c r="J128" s="5">
-        <f>H128/E128</f>
-        <v/>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>226.51</v>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v>67.41330000000001</v>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v>121.7522</v>
-      </c>
-      <c r="N128" s="6">
-        <f>J128/M128-1</f>
-        <v/>
-      </c>
-      <c r="O128" s="6">
-        <f>J128/K128-1</f>
-        <v/>
-      </c>
-      <c r="P128" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>529921</v>
-      </c>
-      <c r="B129" s="2" t="inlineStr"/>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>7908134200453</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>SLINDA 4MG CX 24 COMP REV+4 PLACEBOS</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>92.04650000000001</v>
-      </c>
-      <c r="I129" s="5">
-        <f>G129*H129</f>
-        <v/>
-      </c>
-      <c r="J129" s="5">
-        <f>H129/E129</f>
-        <v/>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>95.08</v>
-      </c>
-      <c r="L129" s="5" t="n">
-        <v>89.83499999999999</v>
-      </c>
-      <c r="M129" s="5" t="n">
-        <v>91.58333333333333</v>
-      </c>
-      <c r="N129" s="6">
-        <f>J129/M129-1</f>
-        <v/>
-      </c>
-      <c r="O129" s="6">
-        <f>J129/K129-1</f>
-        <v/>
-      </c>
-      <c r="P129" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>558381</v>
-      </c>
-      <c r="B130" s="2" t="inlineStr"/>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>7896902212152</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>SOLUCAO SORIMAX 100 ML</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G130" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I130" s="5">
-        <f>G130*H130</f>
-        <v/>
-      </c>
-      <c r="J130" s="5">
-        <f>H130/E130</f>
-        <v/>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L130" s="5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="M130" s="5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N130" s="6">
-        <f>J130/M130-1</f>
-        <v/>
-      </c>
-      <c r="O130" s="6">
-        <f>J130/K130-1</f>
-        <v/>
-      </c>
-      <c r="P130" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>264541</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr"/>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>7894916512107</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>SOMALGIN CARDIO 81MG 6 BLT 10 COMP REV-S</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>24.0045</v>
-      </c>
-      <c r="I131" s="5">
-        <f>G131*H131</f>
-        <v/>
-      </c>
-      <c r="J131" s="5">
-        <f>H131/E131</f>
-        <v/>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>21.925</v>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="N131" s="6">
-        <f>J131/M131-1</f>
-        <v/>
-      </c>
-      <c r="O131" s="6">
-        <f>J131/K131-1</f>
-        <v/>
-      </c>
-      <c r="P131" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +4.8% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>661151</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr"/>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>7899852025469</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>SPR VULT RECARGA HIDRT 100ML-DEMAIS PROD</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="I132" s="5">
-        <f>G132*H132</f>
-        <v/>
-      </c>
-      <c r="J132" s="5">
-        <f>H132/E132</f>
-        <v/>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v>27.51</v>
-      </c>
-      <c r="N132" s="6">
-        <f>J132/M132-1</f>
-        <v/>
-      </c>
-      <c r="O132" s="6">
-        <f>J132/K132-1</f>
-        <v/>
-      </c>
-      <c r="P132" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>624141</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr"/>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>7506339305142</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>TESTE GRAV CLEARBLUE PLUS 2UNI-DEMAIS PROD</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G133" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="I133" s="5">
-        <f>G133*H133</f>
-        <v/>
-      </c>
-      <c r="J133" s="5">
-        <f>H133/E133</f>
-        <v/>
-      </c>
-      <c r="K133" s="5" t="n">
-        <v>24.7675</v>
-      </c>
-      <c r="L133" s="5" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v>24.215</v>
-      </c>
-      <c r="N133" s="6">
-        <f>J133/M133-1</f>
-        <v/>
-      </c>
-      <c r="O133" s="6">
-        <f>J133/K133-1</f>
-        <v/>
-      </c>
-      <c r="P133" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>622921</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr"/>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>7500435137959</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>TESTE GRAV CLEARBLUE SAIBA ANTES-DEMAIS PROD</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G134" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>18.753</v>
-      </c>
-      <c r="I134" s="5">
-        <f>G134*H134</f>
-        <v/>
-      </c>
-      <c r="J134" s="5">
-        <f>H134/E134</f>
-        <v/>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v>20.60666666666667</v>
-      </c>
-      <c r="N134" s="6">
-        <f>J134/M134-1</f>
-        <v/>
-      </c>
-      <c r="O134" s="6">
-        <f>J134/K134-1</f>
-        <v/>
-      </c>
-      <c r="P134" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>610651</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr"/>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>7908032300866</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>TOALHAS UMED PIQUITUCHO PRATIC C/48UND</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G135" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>4.0255</v>
-      </c>
-      <c r="I135" s="5">
-        <f>G135*H135</f>
-        <v/>
-      </c>
-      <c r="J135" s="5">
-        <f>H135/E135</f>
-        <v/>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="N135" s="6">
-        <f>J135/M135-1</f>
-        <v/>
-      </c>
-      <c r="O135" s="6">
-        <f>J135/K135-1</f>
-        <v/>
-      </c>
-      <c r="P135" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>319341</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr"/>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>7891045008433</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>V - NORDETTE 0,15+0,03MG CX 21 DRG</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G136" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>9.927499999999998</v>
-      </c>
-      <c r="I136" s="5">
-        <f>G136*H136</f>
-        <v/>
-      </c>
-      <c r="J136" s="5">
-        <f>H136/E136</f>
-        <v/>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v>9.265000000000001</v>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v>9.831666666666667</v>
-      </c>
-      <c r="N136" s="6">
-        <f>J136/M136-1</f>
-        <v/>
-      </c>
-      <c r="O136" s="6">
-        <f>J136/K136-1</f>
-        <v/>
-      </c>
-      <c r="P136" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>654331</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr"/>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>7891653014260</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>VAGISIL DEO INTIMO JASMIN BRANCO 75ML</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="I137" s="5">
-        <f>G137*H137</f>
-        <v/>
-      </c>
-      <c r="J137" s="5">
-        <f>H137/E137</f>
-        <v/>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="L137" s="5" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="M137" s="5" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="N137" s="6">
-        <f>J137/M137-1</f>
-        <v/>
-      </c>
-      <c r="O137" s="6">
-        <f>J137/K137-1</f>
-        <v/>
-      </c>
-      <c r="P137" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +5.3% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>662301</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr"/>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>7891653014031</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>VAGISIL DEO INTIMO ODOR BLOCK 60ML</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="I138" s="5">
-        <f>G138*H138</f>
-        <v/>
-      </c>
-      <c r="J138" s="5">
-        <f>H138/E138</f>
-        <v/>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v>22.42</v>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v>22.42666666666667</v>
-      </c>
-      <c r="N138" s="6">
-        <f>J138/M138-1</f>
-        <v/>
-      </c>
-      <c r="O138" s="6">
-        <f>J138/K138-1</f>
-        <v/>
-      </c>
-      <c r="P138" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>654311</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr"/>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>7891653040078</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>VAGISIL SAB INTIMO URIN PROTECT 300ML</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G139" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="I139" s="5">
-        <f>G139*H139</f>
-        <v/>
-      </c>
-      <c r="J139" s="5">
-        <f>H139/E139</f>
-        <v/>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>21.68</v>
-      </c>
-      <c r="L139" s="5" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="M139" s="5" t="n">
-        <v>20.43666666666667</v>
-      </c>
-      <c r="N139" s="6">
-        <f>J139/M139-1</f>
-        <v/>
-      </c>
-      <c r="O139" s="6">
-        <f>J139/K139-1</f>
-        <v/>
-      </c>
-      <c r="P139" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>621491</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr"/>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>7896004789545</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>VENCIDO - LEFOR 2,5MG CX 30 COMP</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>46.73175</v>
-      </c>
-      <c r="I140" s="5">
-        <f>G140*H140</f>
-        <v/>
-      </c>
-      <c r="J140" s="5">
-        <f>H140/E140</f>
-        <v/>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>42.835</v>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v>42.835</v>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v>42.835</v>
-      </c>
-      <c r="N140" s="6">
-        <f>J140/M140-1</f>
-        <v/>
-      </c>
-      <c r="O140" s="6">
-        <f>J140/K140-1</f>
-        <v/>
-      </c>
-      <c r="P140" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +9.1% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>635041</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr"/>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>7899852025520</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>VULT HAIR CO CACHOS 325ML</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="I141" s="5">
-        <f>G141*H141</f>
-        <v/>
-      </c>
-      <c r="J141" s="5">
-        <f>H141/E141</f>
-        <v/>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="L141" s="5" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M141" s="5" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N141" s="6">
-        <f>J141/M141-1</f>
-        <v/>
-      </c>
-      <c r="O141" s="6">
-        <f>J141/K141-1</f>
-        <v/>
-      </c>
-      <c r="P141" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +7.4% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>635051</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr"/>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>7899852025506</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>VULT HAIR CO LISOS 325ML</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H142" s="5" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="I142" s="5">
-        <f>G142*H142</f>
-        <v/>
-      </c>
-      <c r="J142" s="5">
-        <f>H142/E142</f>
-        <v/>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="L142" s="5" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="N142" s="6">
-        <f>J142/M142-1</f>
-        <v/>
-      </c>
-      <c r="O142" s="6">
-        <f>J142/K142-1</f>
-        <v/>
-      </c>
-      <c r="P142" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +8.4% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I143" s="8">
-        <f>SUM(I2:I142)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>Pedido FINAL NAZARIA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: preço até 5% acima da referência (últ. compra; sem ela, menor histórico), 10% quando o item está zerado. 'Qtd pedido' na embalagem do fornecedor.</t>
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Pedido FINAL NAZARIA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
       </c>
     </row>

--- a/cotacoes/2026-09-08/fechamento/PEDIDO_NAZARIA_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_NAZARIA_09-09-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:Q117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1276,30 +1276,30 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>477961</v>
+        <v>653061</v>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>7894916508377</t>
+          <t>7897947620520</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>BRASART HCT 320+25MG CX 30 COMP REV</t>
+          <t>CARMED ENXAG BUC FR 250ML SBR BEIJOS</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>88.33499999999999</v>
+        <v>19.56</v>
       </c>
       <c r="I14" s="5">
         <f>G14*H14</f>
@@ -1309,43 +1309,31 @@
         <f>H14/E14</f>
         <v/>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>89.44</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>79.81999999999999</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>84.42666666666666</v>
-      </c>
-      <c r="N14" s="6">
-        <f>J14/M14-1</f>
-        <v/>
-      </c>
-      <c r="O14" s="6">
-        <f>J14/K14-1</f>
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>477941</v>
+        <v>662881</v>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>7894916508346</t>
+          <t>7897947620605</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BRASART HCT 80+12,5MG CX 30 COMP REV</t>
+          <t>CARMED GLITTER BG 10G 3 EM 1</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1358,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>75.50399999999999</v>
+        <v>27.24</v>
       </c>
       <c r="I15" s="5">
         <f>G15*H15</f>
@@ -1368,56 +1356,44 @@
         <f>H15/E15</f>
         <v/>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>76.45</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>70.33</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>74.14333333333333</v>
-      </c>
-      <c r="N15" s="6">
-        <f>J15/M15-1</f>
-        <v/>
-      </c>
-      <c r="O15" s="6">
-        <f>J15/K15-1</f>
-        <v/>
-      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>653061</v>
+        <v>576441</v>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>7897947620520</t>
+          <t>7891150045347</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CARMED ENXAG BUC FR 250ML SBR BEIJOS</t>
+          <t>CONDIC.DOVE BABY CAB.CLA.200M</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>19.56</v>
+        <v>14.9</v>
       </c>
       <c r="I16" s="5">
         <f>G16*H16</f>
@@ -1427,31 +1403,43 @@
         <f>H16/E16</f>
         <v/>
       </c>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
+      <c r="K16" s="5" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="N16" s="6">
+        <f>J16/M16-1</f>
+        <v/>
+      </c>
+      <c r="O16" s="6">
+        <f>J16/K16-1</f>
+        <v/>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>662881</v>
+        <v>1943</v>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7897947620605</t>
+          <t>7891150086210</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CARMED GLITTER BG 10G 3 EM 1</t>
+          <t>CR D CLOSE UP GEL MENTA 130G</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1464,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>27.24</v>
+        <v>3.87</v>
       </c>
       <c r="I17" s="5">
         <f>G17*H17</f>
@@ -1474,44 +1462,56 @@
         <f>H17/E17</f>
         <v/>
       </c>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
+      <c r="K17" s="5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N17" s="6">
+        <f>J17/M17-1</f>
+        <v/>
+      </c>
+      <c r="O17" s="6">
+        <f>J17/K17-1</f>
+        <v/>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>REAJUSTE +0.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>576441</v>
+        <v>637691</v>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>7891150045347</t>
+          <t>7891150094949</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CONDIC.DOVE BABY CAB.CLA.200M</t>
+          <t>CR TRAT DOVE HIDRATACAO 270G</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>14.9</v>
+        <v>34.7</v>
       </c>
       <c r="I18" s="5">
         <f>G18*H18</f>
@@ -1522,13 +1522,13 @@
         <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>14.97</v>
+        <v>40.79</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>14.97</v>
+        <v>40.79</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>14.97</v>
+        <v>40.79</v>
       </c>
       <c r="N18" s="6">
         <f>J18/M18-1</f>
@@ -1547,30 +1547,30 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1943</v>
+        <v>653591</v>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7891150086210</t>
+          <t>7896438200906</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CR D CLOSE UP GEL MENTA 130G</t>
+          <t>CREATINA PROBIOTICA 300G</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>3.87</v>
+        <v>40.37</v>
       </c>
       <c r="I19" s="5">
         <f>G19*H19</f>
@@ -1581,13 +1581,13 @@
         <v/>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3.86</v>
+        <v>40.37</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>3.86</v>
+        <v>40.37</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>3.86</v>
+        <v>40.37</v>
       </c>
       <c r="N19" s="6">
         <f>J19/M19-1</f>
@@ -1599,37 +1599,37 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.3% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>637691</v>
+        <v>630671</v>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>7891150094949</t>
+          <t>7898108640746</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CR TRAT DOVE HIDRATACAO 270G</t>
+          <t>CURATIVO CICATRISAN KURA DODOI CX 20 UND</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>34.7</v>
+        <v>5.016</v>
       </c>
       <c r="I20" s="5">
         <f>G20*H20</f>
@@ -1640,13 +1640,13 @@
         <v/>
       </c>
       <c r="K20" s="5" t="n">
-        <v>40.79</v>
+        <v>5.42</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>40.79</v>
+        <v>5.42</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>40.79</v>
+        <v>5.419999999999999</v>
       </c>
       <c r="N20" s="6">
         <f>J20/M20-1</f>
@@ -1665,30 +1665,30 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>653591</v>
+        <v>833</v>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>7896438200906</t>
+          <t>7891800540406</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CREATINA PROBIOTICA 300G</t>
+          <t>CURATIVO CREMER MINIONS 10UN</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>40.37</v>
+        <v>4.462</v>
       </c>
       <c r="I21" s="5">
         <f>G21*H21</f>
@@ -1699,13 +1699,13 @@
         <v/>
       </c>
       <c r="K21" s="5" t="n">
-        <v>40.37</v>
+        <v>4.59</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>40.37</v>
+        <v>4.59</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>40.37</v>
+        <v>4.59</v>
       </c>
       <c r="N21" s="6">
         <f>J21/M21-1</f>
@@ -1724,30 +1724,30 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>630671</v>
+        <v>631611</v>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>7898108640746</t>
+          <t>7896544925496</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO CICATRISAN KURA DODOI CX 20 UND</t>
+          <t>CURATIVO FLEXIVEL SHOW DA LUNA  C/10UN.</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>5.016</v>
+        <v>3.06</v>
       </c>
       <c r="I22" s="5">
         <f>G22*H22</f>
@@ -1758,13 +1758,13 @@
         <v/>
       </c>
       <c r="K22" s="5" t="n">
-        <v>5.42</v>
+        <v>3.06</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>5.42</v>
+        <v>3.06</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>5.419999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="N22" s="6">
         <f>J22/M22-1</f>
@@ -1779,34 +1779,38 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (2 un)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>833</v>
+        <v>669911</v>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>7891800540406</t>
+          <t>7891150100503</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO CREMER MINIONS 10UN</t>
+          <t>DEO REXONA WOMEN AER INV 150ML   UNIL %DN:12.00</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>4.462</v>
+        <v>15.18</v>
       </c>
       <c r="I23" s="5">
         <f>G23*H23</f>
@@ -1817,13 +1821,13 @@
         <v/>
       </c>
       <c r="K23" s="5" t="n">
-        <v>4.59</v>
+        <v>16.62</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>4.59</v>
+        <v>13.53</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>4.59</v>
+        <v>15.59</v>
       </c>
       <c r="N23" s="6">
         <f>J23/M23-1</f>
@@ -1842,30 +1846,30 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>631611</v>
+        <v>6581</v>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>7896544925496</t>
+          <t>7891268101799</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CURATIVO FLEXIVEL SHOW DA LUNA  C/10UN.</t>
+          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>3.06</v>
+        <v>35.4825</v>
       </c>
       <c r="I24" s="5">
         <f>G24*H24</f>
@@ -1876,13 +1880,13 @@
         <v/>
       </c>
       <c r="K24" s="5" t="n">
-        <v>3.06</v>
+        <v>36.87</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>3.06</v>
+        <v>33.56</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>3.06</v>
+        <v>34.68</v>
       </c>
       <c r="N24" s="6">
         <f>J24/M24-1</f>
@@ -1897,38 +1901,34 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (2 un)</t>
-        </is>
-      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>669911</v>
+        <v>6601</v>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>7891150100503</t>
+          <t>7891268101782</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DEO REXONA WOMEN AER INV 150ML   UNIL %DN:12.00</t>
+          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML+1SER PREENCH</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>15.18</v>
+        <v>45.98</v>
       </c>
       <c r="I25" s="5">
         <f>G25*H25</f>
@@ -1939,13 +1939,13 @@
         <v/>
       </c>
       <c r="K25" s="5" t="n">
-        <v>16.62</v>
+        <v>46.77</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>13.53</v>
+        <v>41.6</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>15.59</v>
+        <v>43.87333333333333</v>
       </c>
       <c r="N25" s="6">
         <f>J25/M25-1</f>
@@ -1964,30 +1964,30 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6581</v>
+        <v>645431</v>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>7891268101799</t>
+          <t>7891058018238</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML</t>
+          <t>DERMACYD FEM 200+100ML</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>35.4825</v>
+        <v>25.11</v>
       </c>
       <c r="I26" s="5">
         <f>G26*H26</f>
@@ -1998,13 +1998,13 @@
         <v/>
       </c>
       <c r="K26" s="5" t="n">
-        <v>36.87</v>
+        <v>25.16</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>33.56</v>
+        <v>25.06</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>34.68</v>
+        <v>25.12666666666667</v>
       </c>
       <c r="N26" s="6">
         <f>J26/M26-1</f>
@@ -2019,21 +2019,25 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (1 un)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6601</v>
+        <v>591811</v>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>7891268101782</t>
+          <t>78924352</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DEPO PROVERA 150MG SUS INJ 1FA X 1ML+1SER PREENCH</t>
+          <t>DES R-ON REXONA W.COTTON 50ML</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2046,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>45.98</v>
+        <v>8.27</v>
       </c>
       <c r="I27" s="5">
         <f>G27*H27</f>
@@ -2057,13 +2061,13 @@
         <v/>
       </c>
       <c r="K27" s="5" t="n">
-        <v>46.77</v>
+        <v>7.9967</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>41.6</v>
+        <v>7.9967</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>43.87333333333333</v>
+        <v>7.9967</v>
       </c>
       <c r="N27" s="6">
         <f>J27/M27-1</f>
@@ -2075,37 +2079,37 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>645431</v>
+        <v>539561</v>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>7891058018238</t>
+          <t>7891106913966</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DERMACYD FEM 200+100ML</t>
+          <t>DIANE 35 2+0,035MG CX 21 DRG</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>25.11</v>
+        <v>31.1904</v>
       </c>
       <c r="I28" s="5">
         <f>G28*H28</f>
@@ -2116,13 +2120,13 @@
         <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>25.16</v>
+        <v>32.08</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>25.06</v>
+        <v>27.875</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>25.12666666666667</v>
+        <v>30.225</v>
       </c>
       <c r="N28" s="6">
         <f>J28/M28-1</f>
@@ -2137,25 +2141,21 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un)</t>
-        </is>
-      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>591811</v>
+        <v>648781</v>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>78924352</t>
+          <t>7891150021662</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DES R-ON REXONA W.COTTON 50ML</t>
+          <t>DOVE SH 200ML MEN 2EM1 FORCA RESISTEN M3</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>8.27</v>
+        <v>15.97</v>
       </c>
       <c r="I29" s="5">
         <f>G29*H29</f>
@@ -2179,13 +2179,13 @@
         <v/>
       </c>
       <c r="K29" s="5" t="n">
-        <v>7.9967</v>
+        <v>15.4</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>7.9967</v>
+        <v>15.4</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>7.9967</v>
+        <v>15.4</v>
       </c>
       <c r="N29" s="6">
         <f>J29/M29-1</f>
@@ -2197,37 +2197,37 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.4% vs últ. (≤4%)</t>
+          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>539561</v>
+        <v>648591</v>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>7891106913966</t>
+          <t>7891150021709</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DIANE 35 2+0,035MG CX 21 DRG</t>
+          <t>DOVE SH 200ML MEN PROTECAO ANTICASPA M3</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>31.1904</v>
+        <v>15.97</v>
       </c>
       <c r="I30" s="5">
         <f>G30*H30</f>
@@ -2238,13 +2238,13 @@
         <v/>
       </c>
       <c r="K30" s="5" t="n">
-        <v>32.08</v>
+        <v>15.4</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>27.875</v>
+        <v>15.4</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>30.225</v>
+        <v>15.4</v>
       </c>
       <c r="N30" s="6">
         <f>J30/M30-1</f>
@@ -2256,24 +2256,24 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>648781</v>
+        <v>452521</v>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>7891150021662</t>
+          <t>7898109240136</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DOVE SH 200ML MEN 2EM1 FORCA RESISTEN M3</t>
+          <t>ELOTIN SOL OTO FR GTS 5ML</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>15.97</v>
+        <v>9.490500000000001</v>
       </c>
       <c r="I31" s="5">
         <f>G31*H31</f>
@@ -2297,13 +2297,13 @@
         <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>15.4</v>
+        <v>8.99</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>15.4</v>
+        <v>8.99</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>15.4</v>
+        <v>8.99</v>
       </c>
       <c r="N31" s="6">
         <f>J31/M31-1</f>
@@ -2315,24 +2315,24 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
+          <t>REAJUSTE +5.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>648591</v>
+        <v>594331</v>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>7891150021709</t>
+          <t>070942005111</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DOVE SH 200ML MEN PROTECAO ANTICASPA M3</t>
+          <t>ESC INTERDENTAL GUMSOFT PICK</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>15.97</v>
+        <v>21.5616</v>
       </c>
       <c r="I32" s="5">
         <f>G32*H32</f>
@@ -2356,13 +2356,13 @@
         <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>15.4</v>
+        <v>21.99</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>15.4</v>
+        <v>21.99</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>15.4</v>
+        <v>21.99</v>
       </c>
       <c r="N32" s="6">
         <f>J32/M32-1</f>
@@ -2374,24 +2374,28 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>preços divergentes entre EANs (usado menor)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>452521</v>
+        <v>702501</v>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>7898109240136</t>
+          <t>7899026415478</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ELOTIN SOL OTO FR GTS 5ML</t>
+          <t>ESM COL_CREM JABUTICABA</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2404,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>9.490500000000001</v>
+        <v>5.35</v>
       </c>
       <c r="I33" s="5">
         <f>G33*H33</f>
@@ -2415,13 +2419,13 @@
         <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>8.99</v>
+        <v>5.93</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>8.99</v>
+        <v>5.93</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>8.99</v>
+        <v>5.93</v>
       </c>
       <c r="N33" s="6">
         <f>J33/M33-1</f>
@@ -2433,37 +2437,37 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.6% vs média (≤6%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>594331</v>
+        <v>651561</v>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>070942005111</t>
+          <t>7891800669299</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ESC INTERDENTAL GUMSOFT PICK</t>
+          <t>ESPARADRAPO CREMER BEGE 1,2CMX3M   CREM %DN:11.00</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>21.5616</v>
+        <v>3.492</v>
       </c>
       <c r="I34" s="5">
         <f>G34*H34</f>
@@ -2474,13 +2478,13 @@
         <v/>
       </c>
       <c r="K34" s="5" t="n">
-        <v>21.99</v>
+        <v>3.59</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>21.99</v>
+        <v>3.59</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>21.99</v>
+        <v>3.59</v>
       </c>
       <c r="N34" s="6">
         <f>J34/M34-1</f>
@@ -2495,38 +2499,34 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>preços divergentes entre EANs (usado menor)</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>702501</v>
+        <v>578121</v>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>7899026415478</t>
+          <t>7891800628432</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ESM COL_CREM JABUTICABA</t>
+          <t>ESPARADRAPO SALVELOX 5CMX4,5M</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>5.35</v>
+        <v>6.6542</v>
       </c>
       <c r="I35" s="5">
         <f>G35*H35</f>
@@ -2537,13 +2537,13 @@
         <v/>
       </c>
       <c r="K35" s="5" t="n">
-        <v>5.93</v>
+        <v>6.844</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>5.93</v>
+        <v>6.48</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>5.93</v>
+        <v>6.722666666666666</v>
       </c>
       <c r="N35" s="6">
         <f>J35/M35-1</f>
@@ -2562,17 +2562,17 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>235621</v>
+        <v>613831</v>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>7894916510202</t>
+          <t>7896902234093</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ESOGASTRO IBP KIT 14ESO 14CLA 28AMOX+28ESO-S</t>
+          <t>FARMAIODINE PVPI 10% 100ML</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -2585,7 +2585,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>272.07375</v>
+        <v>6.27</v>
       </c>
       <c r="I36" s="5">
         <f>G36*H36</f>
@@ -2596,13 +2596,13 @@
         <v/>
       </c>
       <c r="K36" s="5" t="n">
-        <v>272.59</v>
+        <v>7.09</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>242.54</v>
+        <v>7.09</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>261.6066666666666</v>
+        <v>7.09</v>
       </c>
       <c r="N36" s="6">
         <f>J36/M36-1</f>
@@ -2621,30 +2621,30 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>651561</v>
+        <v>430141</v>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>7891800669299</t>
+          <t>7896014673124</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ESPARADRAPO CREMER BEGE 1,2CMX3M   CREM %DN:11.00</t>
+          <t>FERROPURUM 20 MG/ML SOL INJ 5 AMP 5ML</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>3.492</v>
+        <v>67.81409699999999</v>
       </c>
       <c r="I37" s="5">
         <f>G37*H37</f>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="K37" s="5" t="n">
-        <v>3.59</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>3.59</v>
+        <v>51.6738</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>3.59</v>
+        <v>57.70143333333333</v>
       </c>
       <c r="N37" s="6">
         <f>J37/M37-1</f>
@@ -2680,30 +2680,30 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>578121</v>
+        <v>616361</v>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>7891800628432</t>
+          <t>7896523201504</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ESPARADRAPO SALVELOX 5CMX4,5M</t>
+          <t>FIGMED 200MG CAPS C/30</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>6.6542</v>
+        <v>30.53</v>
       </c>
       <c r="I38" s="5">
         <f>G38*H38</f>
@@ -2714,13 +2714,13 @@
         <v/>
       </c>
       <c r="K38" s="5" t="n">
-        <v>6.844</v>
+        <v>35.69</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>6.48</v>
+        <v>31.99</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>6.722666666666666</v>
+        <v>33.83333333333333</v>
       </c>
       <c r="N38" s="6">
         <f>J38/M38-1</f>
@@ -2739,17 +2739,17 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>613831</v>
+        <v>249121</v>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7896902234093</t>
+          <t>7896523227542</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>FARMAIODINE PVPI 10% 100ML</t>
+          <t>FINASTERIDA 1MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -2762,7 +2762,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>6.27</v>
+        <v>62.28</v>
       </c>
       <c r="I39" s="5">
         <f>G39*H39</f>
@@ -2772,56 +2772,44 @@
         <f>H39/E39</f>
         <v/>
       </c>
-      <c r="K39" s="5" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="N39" s="6">
-        <f>J39/M39-1</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>J39/K39-1</f>
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="6" t="n"/>
+      <c r="O39" s="6" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>430141</v>
+        <v>596631</v>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>7896014673124</t>
+          <t>7891800665529</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>FERROPURUM 20 MG/ML SOL INJ 5 AMP 5ML</t>
+          <t>FITA MICROPOROSA SALVELOX 1,2CMX4,5M</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>67.81409699999999</v>
+        <v>2.7257</v>
       </c>
       <c r="I40" s="5">
         <f>G40*H40</f>
@@ -2832,13 +2820,13 @@
         <v/>
       </c>
       <c r="K40" s="5" t="n">
-        <v>69.76000000000001</v>
+        <v>2.8038</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>51.6738</v>
+        <v>2.65</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>57.70143333333333</v>
+        <v>2.752533333333333</v>
       </c>
       <c r="N40" s="6">
         <f>J40/M40-1</f>
@@ -2857,30 +2845,30 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>616361</v>
+        <v>614481</v>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>7896523201504</t>
+          <t>7896007551279</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>FIGMED 200MG CAPS C/30</t>
+          <t>FRA HUGGIES CARE ROUP HIPER XXG C/48</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>30.53</v>
+        <v>89.83</v>
       </c>
       <c r="I41" s="5">
         <f>G41*H41</f>
@@ -2891,13 +2879,13 @@
         <v/>
       </c>
       <c r="K41" s="5" t="n">
-        <v>35.69</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>31.99</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>33.83333333333333</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="N41" s="6">
         <f>J41/M41-1</f>
@@ -2909,37 +2897,37 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>249121</v>
+        <v>614451</v>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>7896523227542</t>
+          <t>7896007549719</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>FINASTERIDA 1MG CX 30 COMP REV</t>
+          <t>FRA HUGGIES SP CARE ROUP HIPER GDE C/60</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>62.28</v>
+        <v>89.83</v>
       </c>
       <c r="I42" s="5">
         <f>G42*H42</f>
@@ -2949,44 +2937,56 @@
         <f>H42/E42</f>
         <v/>
       </c>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="6" t="n"/>
-      <c r="O42" s="6" t="n"/>
+      <c r="K42" s="5" t="n">
+        <v>87.53619999999999</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>87.53619999999999</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>87.53619999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <f>J42/M42-1</f>
+        <v/>
+      </c>
+      <c r="O42" s="6">
+        <f>J42/K42-1</f>
+        <v/>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>596631</v>
+        <v>614461</v>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>7891800665529</t>
+          <t>7896007551262</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>FITA MICROPOROSA SALVELOX 1,2CMX4,5M</t>
+          <t>FRA HUGGIES SP CARE ROUP HIPER MED C/72</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>2.7257</v>
+        <v>89.83</v>
       </c>
       <c r="I43" s="5">
         <f>G43*H43</f>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="K43" s="5" t="n">
-        <v>2.8038</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>2.65</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>2.752533333333333</v>
+        <v>87.53619999999999</v>
       </c>
       <c r="N43" s="6">
         <f>J43/M43-1</f>
@@ -3015,37 +3015,37 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>614481</v>
+        <v>617081</v>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>7896007551279</t>
+          <t>7896007553051</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES CARE ROUP HIPER XXG C/48</t>
+          <t>FRA HUGGIES TRIPLA ROUP MEGA - GDE C/28</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>89.83</v>
+        <v>37.88</v>
       </c>
       <c r="I44" s="5">
         <f>G44*H44</f>
@@ -3056,13 +3056,13 @@
         <v/>
       </c>
       <c r="K44" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="N44" s="6">
         <f>J44/M44-1</f>
@@ -3074,37 +3074,37 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
+          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>614451</v>
+        <v>616531</v>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>7896007549719</t>
+          <t>7896007553068</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES SP CARE ROUP HIPER GDE C/60</t>
+          <t>FRA HUGGIES TRIPLA ROUP MEGA - XG C/24</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>89.83</v>
+        <v>37.88</v>
       </c>
       <c r="I45" s="5">
         <f>G45*H45</f>
@@ -3115,13 +3115,13 @@
         <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>36.98</v>
       </c>
       <c r="N45" s="6">
         <f>J45/M45-1</f>
@@ -3133,37 +3133,37 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
+          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>614461</v>
+        <v>572481</v>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>7896007551262</t>
+          <t>7896064486170</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES SP CARE ROUP HIPER MED C/72</t>
+          <t>FRALDA GERIAMAX G 7 UN</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>89.83</v>
+        <v>16.36</v>
       </c>
       <c r="I46" s="5">
         <f>G46*H46</f>
@@ -3174,13 +3174,13 @@
         <v/>
       </c>
       <c r="K46" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>87.53619999999999</v>
+        <v>18.17</v>
       </c>
       <c r="N46" s="6">
         <f>J46/M46-1</f>
@@ -3192,37 +3192,37 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>617081</v>
+        <v>572501</v>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>7896007553051</t>
+          <t>7896064486163</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES TRIPLA ROUP MEGA - GDE C/28</t>
+          <t>FRALDA GERIAMAX M 8 UN</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>37.88</v>
+        <v>16.36</v>
       </c>
       <c r="I47" s="5">
         <f>G47*H47</f>
@@ -3233,13 +3233,13 @@
         <v/>
       </c>
       <c r="K47" s="5" t="n">
-        <v>36.98</v>
+        <v>18.26</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>36.98</v>
+        <v>18.17</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>36.98</v>
+        <v>18.17</v>
       </c>
       <c r="N47" s="6">
         <f>J47/M47-1</f>
@@ -3251,24 +3251,24 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>616531</v>
+        <v>631061</v>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>7896007553068</t>
+          <t>7896007549269</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>FRA HUGGIES TRIPLA ROUP MEGA - XG C/24</t>
+          <t>FRALDA HUGGIES TRIPLA HIPER G 78UN</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -3281,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>37.88</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="I48" s="5">
         <f>G48*H48</f>
@@ -3292,13 +3292,13 @@
         <v/>
       </c>
       <c r="K48" s="5" t="n">
-        <v>36.98</v>
+        <v>88.23</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>36.98</v>
+        <v>88.23</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>36.98</v>
+        <v>88.23</v>
       </c>
       <c r="N48" s="6">
         <f>J48/M48-1</f>
@@ -3310,24 +3310,24 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>572481</v>
+        <v>556021</v>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>7896064486170</t>
+          <t>7896007549702</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>FRALDA GERIAMAX G 7 UN</t>
+          <t>FRALDA SHORTINHO HUGGIES SUPREME CARE XXG 24UN</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -3340,7 +3340,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>16.36</v>
+        <v>51.34</v>
       </c>
       <c r="I49" s="5">
         <f>G49*H49</f>
@@ -3351,13 +3351,13 @@
         <v/>
       </c>
       <c r="K49" s="5" t="n">
-        <v>18.17</v>
+        <v>50.0233</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>18.17</v>
+        <v>50.0233</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>18.17</v>
+        <v>50.0233</v>
       </c>
       <c r="N49" s="6">
         <f>J49/M49-1</f>
@@ -3369,37 +3369,37 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>572501</v>
+        <v>670571</v>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>7896064486163</t>
+          <t>7898216368037</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>FRALDA GERIAMAX M 8 UN</t>
+          <t>GARDENAL 100MG C/20 COMP (C1)-REFERENCIA</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>16.36</v>
+        <v>9.468</v>
       </c>
       <c r="I50" s="5">
         <f>G50*H50</f>
@@ -3410,13 +3410,13 @@
         <v/>
       </c>
       <c r="K50" s="5" t="n">
-        <v>18.26</v>
+        <v>9.4094</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>18.17</v>
+        <v>9.4094</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>18.17</v>
+        <v>9.4094</v>
       </c>
       <c r="N50" s="6">
         <f>J50/M50-1</f>
@@ -3428,37 +3428,37 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +0.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>631061</v>
+        <v>630831</v>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>7896007549269</t>
+          <t>7899706178129</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>FRALDA HUGGIES TRIPLA HIPER G 78UN</t>
+          <t>GARNIER AGUA MICELAR 400ML TUDO EM 1</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>86.56999999999999</v>
+        <v>45.67</v>
       </c>
       <c r="I51" s="5">
         <f>G51*H51</f>
@@ -3469,13 +3469,13 @@
         <v/>
       </c>
       <c r="K51" s="5" t="n">
-        <v>88.23</v>
+        <v>44.69</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>88.23</v>
+        <v>44.69</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>88.23</v>
+        <v>44.69</v>
       </c>
       <c r="N51" s="6">
         <f>J51/M51-1</f>
@@ -3487,37 +3487,37 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>556021</v>
+        <v>189141</v>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>7896007549702</t>
+          <t>7891106003230</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FRALDA SHORTINHO HUGGIES SUPREME CARE XXG 24UN</t>
+          <t>GINO CANESTEN 20 MG/G CREME VAG BG 20G+3APLIC</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>51.34</v>
+        <v>73.19619999999999</v>
       </c>
       <c r="I52" s="5">
         <f>G52*H52</f>
@@ -3528,13 +3528,13 @@
         <v/>
       </c>
       <c r="K52" s="5" t="n">
-        <v>50.0233</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>50.0233</v>
+        <v>65.23</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>50.0233</v>
+        <v>67.52166666666666</v>
       </c>
       <c r="N52" s="6">
         <f>J52/M52-1</f>
@@ -3546,37 +3546,37 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
+          <t>REAJUSTE +3.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>670571</v>
+        <v>533121</v>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>7898216368037</t>
+          <t>7891721201806</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>GARDENAL 100MG C/20 COMP (C1)-REFERENCIA</t>
+          <t>GLIFAGE XR 500MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>9.468</v>
+        <v>7.436800000000001</v>
       </c>
       <c r="I53" s="5">
         <f>G53*H53</f>
@@ -3587,13 +3587,13 @@
         <v/>
       </c>
       <c r="K53" s="5" t="n">
-        <v>9.4094</v>
+        <v>7.2626</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>9.4094</v>
+        <v>6.4487</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>9.4094</v>
+        <v>6.711666666666666</v>
       </c>
       <c r="N53" s="6">
         <f>J53/M53-1</f>
@@ -3605,24 +3605,24 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.6% vs últ. (≤4%)</t>
+          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>630831</v>
+        <v>583441</v>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>7899706178129</t>
+          <t>7896512944436</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>GARNIER AGUA MICELAR 400ML TUDO EM 1</t>
+          <t>GRANADO BEBE CR HID 120ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -3635,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>45.67</v>
+        <v>21.32</v>
       </c>
       <c r="I54" s="5">
         <f>G54*H54</f>
@@ -3646,13 +3646,13 @@
         <v/>
       </c>
       <c r="K54" s="5" t="n">
-        <v>44.69</v>
+        <v>21.65</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>44.69</v>
+        <v>21.65</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>44.69</v>
+        <v>21.65</v>
       </c>
       <c r="N54" s="6">
         <f>J54/M54-1</f>
@@ -3664,37 +3664,37 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.2% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>189141</v>
+        <v>626251</v>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>7891106003230</t>
+          <t>070942005142</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>GINO CANESTEN 20 MG/G CREME VAG BG 20G+3APLIC</t>
+          <t>GUM ESC DENTAL MIRACULOUS MANUAL 2UN</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>73.19619999999999</v>
+        <v>14.2176</v>
       </c>
       <c r="I55" s="5">
         <f>G55*H55</f>
@@ -3705,13 +3705,13 @@
         <v/>
       </c>
       <c r="K55" s="5" t="n">
-        <v>70.93000000000001</v>
+        <v>15.265</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>65.23</v>
+        <v>15.265</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>67.52166666666666</v>
+        <v>15.265</v>
       </c>
       <c r="N55" s="6">
         <f>J55/M55-1</f>
@@ -3723,37 +3723,37 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.2% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>533121</v>
+        <v>554541</v>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>7891721201806</t>
+          <t>7908134200040</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>GLIFAGE XR 500MG CX 30 COMP</t>
+          <t>GYNOTRAN 750+200MG OVULO 1 STRIP X 7+14 DEDEIRAS</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>266</v>
+        <v>2</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>266</v>
+        <v>2</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>7.436800000000001</v>
+        <v>87.41460000000001</v>
       </c>
       <c r="I56" s="5">
         <f>G56*H56</f>
@@ -3764,13 +3764,13 @@
         <v/>
       </c>
       <c r="K56" s="5" t="n">
-        <v>7.2626</v>
+        <v>90.84</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>6.4487</v>
+        <v>84.2</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>6.711666666666666</v>
+        <v>88.62666666666667</v>
       </c>
       <c r="N56" s="6">
         <f>J56/M56-1</f>
@@ -3782,24 +3782,24 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.4% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>583441</v>
+        <v>648351</v>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>7896512944436</t>
+          <t>7898108640623</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>GRANADO BEBE CR HID 120ML TRADICIONAL</t>
+          <t>HASTES FLEX SANCARE 75UN</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -3812,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>21.32</v>
+        <v>1.767</v>
       </c>
       <c r="I57" s="5">
         <f>G57*H57</f>
@@ -3823,13 +3823,13 @@
         <v/>
       </c>
       <c r="K57" s="5" t="n">
-        <v>21.65</v>
+        <v>1.8442</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>21.65</v>
+        <v>1.8442</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>21.65</v>
+        <v>1.8442</v>
       </c>
       <c r="N57" s="6">
         <f>J57/M57-1</f>
@@ -3848,17 +3848,17 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>626251</v>
+        <v>598351</v>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>070942005142</t>
+          <t>7896512944443</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>GUM ESC DENTAL MIRACULOUS MANUAL 2UN</t>
+          <t>HID INF GRANADO BEBE 120ML LAVANDA</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>14.2176</v>
+        <v>21.32</v>
       </c>
       <c r="I58" s="5">
         <f>G58*H58</f>
@@ -3882,13 +3882,13 @@
         <v/>
       </c>
       <c r="K58" s="5" t="n">
-        <v>15.265</v>
+        <v>21.65</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>15.265</v>
+        <v>21.65</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>15.265</v>
+        <v>21.65</v>
       </c>
       <c r="N58" s="6">
         <f>J58/M58-1</f>
@@ -3907,30 +3907,30 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>554541</v>
+        <v>284521</v>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>7908134200040</t>
+          <t>7891058002657</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>GYNOTRAN 750+200MG OVULO 1 STRIP X 7+14 DEDEIRAS</t>
+          <t>HIDROCLOROTIAZIDA 25MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>87.41460000000001</v>
+        <v>2.434242</v>
       </c>
       <c r="I59" s="5">
         <f>G59*H59</f>
@@ -3941,13 +3941,13 @@
         <v/>
       </c>
       <c r="K59" s="5" t="n">
-        <v>90.84</v>
+        <v>2.38</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>84.2</v>
+        <v>0.8065</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>88.62666666666667</v>
+        <v>1.8555</v>
       </c>
       <c r="N59" s="6">
         <f>J59/M59-1</f>
@@ -3959,37 +3959,37 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>648351</v>
+        <v>406241</v>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>7898108640623</t>
+          <t>7897411601505</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>HASTES FLEX SANCARE 75UN</t>
+          <t>HIRUDOID 3MG/G GEL BG X 40G</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>1.767</v>
+        <v>32.016</v>
       </c>
       <c r="I60" s="5">
         <f>G60*H60</f>
@@ -4000,13 +4000,13 @@
         <v/>
       </c>
       <c r="K60" s="5" t="n">
-        <v>1.8442</v>
+        <v>32.92</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>1.8442</v>
+        <v>28.79</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>1.8442</v>
+        <v>31.54333333333333</v>
       </c>
       <c r="N60" s="6">
         <f>J60/M60-1</f>
@@ -4025,17 +4025,17 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>598351</v>
+        <v>406261</v>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>7896512944443</t>
+          <t>7897411601567</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>HID INF GRANADO BEBE 120ML LAVANDA</t>
+          <t>HIRUDOID 5MG/G POM BG X 40G</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -4048,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>21.32</v>
+        <v>35.0592</v>
       </c>
       <c r="I61" s="5">
         <f>G61*H61</f>
@@ -4059,13 +4059,13 @@
         <v/>
       </c>
       <c r="K61" s="5" t="n">
-        <v>21.65</v>
+        <v>36.05</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>21.65</v>
+        <v>31.52</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>21.65</v>
+        <v>34.415</v>
       </c>
       <c r="N61" s="6">
         <f>J61/M61-1</f>
@@ -4084,30 +4084,30 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>284521</v>
+        <v>646171</v>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>7891058002657</t>
+          <t>7899941202269</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>HIDROCLOROTIAZIDA 25MG CX 30 COMP</t>
+          <t>HORUS MAX TITANIUM FRUTAS VERMELHAS POTE 150G</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>2.434242</v>
+        <v>38.09</v>
       </c>
       <c r="I62" s="5">
         <f>G62*H62</f>
@@ -4118,13 +4118,13 @@
         <v/>
       </c>
       <c r="K62" s="5" t="n">
-        <v>2.38</v>
+        <v>59.9</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.8065</v>
+        <v>59.9</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>1.8555</v>
+        <v>59.9</v>
       </c>
       <c r="N62" s="6">
         <f>J62/M62-1</f>
@@ -4136,37 +4136,37 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.3% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>406241</v>
+        <v>637531</v>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>7897411601505</t>
+          <t>7897211100192</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 3MG/G GEL BG X 40G</t>
+          <t>K-Y GEL LUBRIF INTIMO 50G</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>32.016</v>
+        <v>19.3</v>
       </c>
       <c r="I63" s="5">
         <f>G63*H63</f>
@@ -4177,13 +4177,13 @@
         <v/>
       </c>
       <c r="K63" s="5" t="n">
-        <v>32.92</v>
+        <v>18.53</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>28.79</v>
+        <v>18.53</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>31.54333333333333</v>
+        <v>18.53</v>
       </c>
       <c r="N63" s="6">
         <f>J63/M63-1</f>
@@ -4195,24 +4195,24 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +4.2% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>406261</v>
+        <v>400901</v>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>7897411601567</t>
+          <t>7896641804397</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>HIRUDOID 5MG/G POM BG X 40G</t>
+          <t>KALOBA 825MG/ML SOL ORAL FR 50ML</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -4225,7 +4225,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>35.0592</v>
+        <v>124.8096</v>
       </c>
       <c r="I64" s="5">
         <f>G64*H64</f>
@@ -4236,13 +4236,13 @@
         <v/>
       </c>
       <c r="K64" s="5" t="n">
-        <v>36.05</v>
+        <v>128.35</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>31.52</v>
+        <v>111.97</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>34.415</v>
+        <v>121.54</v>
       </c>
       <c r="N64" s="6">
         <f>J64/M64-1</f>
@@ -4261,30 +4261,30 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>646171</v>
+        <v>677701</v>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>7899941202269</t>
+          <t>7891150103801</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>HORUS MAX TITANIUM FRUTAS VERMELHAS POTE 150G</t>
+          <t>KIT SH+COND DOVE HIDRAT+HIA 350ML+175ML</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>38.09</v>
+        <v>21.52</v>
       </c>
       <c r="I65" s="5">
         <f>G65*H65</f>
@@ -4295,13 +4295,13 @@
         <v/>
       </c>
       <c r="K65" s="5" t="n">
-        <v>59.9</v>
+        <v>28.36</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>59.9</v>
+        <v>28.36</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>59.9</v>
+        <v>28.36</v>
       </c>
       <c r="N65" s="6">
         <f>J65/M65-1</f>
@@ -4320,30 +4320,30 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>637531</v>
+        <v>22803</v>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>7897211100192</t>
+          <t>4006000101354</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>K-Y GEL LUBRIF INTIMO 50G</t>
+          <t>LABIAL NIVEA HIDRACOLOR VERMEL FPS30 4,8G</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>19.3</v>
+        <v>23.3</v>
       </c>
       <c r="I66" s="5">
         <f>G66*H66</f>
@@ -4354,13 +4354,13 @@
         <v/>
       </c>
       <c r="K66" s="5" t="n">
-        <v>18.53</v>
+        <v>23.18</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>18.53</v>
+        <v>23.18</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>18.53</v>
+        <v>23.18</v>
       </c>
       <c r="N66" s="6">
         <f>J66/M66-1</f>
@@ -4372,24 +4372,24 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.2% vs média (≤6%)</t>
+          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>400901</v>
+        <v>310061</v>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>7896641804397</t>
+          <t>7897411610750</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>KALOBA 825MG/ML SOL ORAL FR 50ML</t>
+          <t>LACTULONA 667MG/ML XPE FR 120ML SB AMEIXA</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -4402,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>124.8096</v>
+        <v>46.8384</v>
       </c>
       <c r="I67" s="5">
         <f>G67*H67</f>
@@ -4413,13 +4413,13 @@
         <v/>
       </c>
       <c r="K67" s="5" t="n">
-        <v>128.35</v>
+        <v>48.17</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>111.97</v>
+        <v>42.12</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>121.54</v>
+        <v>45.98166666666666</v>
       </c>
       <c r="N67" s="6">
         <f>J67/M67-1</f>
@@ -4438,17 +4438,17 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>677701</v>
+        <v>984</v>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>7891150103801</t>
+          <t>7897947621077</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>KIT SH+COND DOVE HIDRAT+HIA 350ML+175ML</t>
+          <t>LAVITAN COMPLEXO B COMP REV FR X 100</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -4461,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>21.52</v>
+        <v>38.97</v>
       </c>
       <c r="I68" s="5">
         <f>G68*H68</f>
@@ -4471,56 +4471,44 @@
         <f>H68/E68</f>
         <v/>
       </c>
-      <c r="K68" s="5" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="N68" s="6">
-        <f>J68/M68-1</f>
-        <v/>
-      </c>
-      <c r="O68" s="6">
-        <f>J68/K68-1</f>
-        <v/>
-      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="6" t="n"/>
+      <c r="O68" s="6" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>22803</v>
+        <v>564641</v>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>4006000101354</t>
+          <t>7897947601147</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>LABIAL NIVEA HIDRACOLOR VERMEL FPS30 4,8G</t>
+          <t>LAVITAN MELATONINA 0,21MG CP PT 90 MOR</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>23.3</v>
+        <v>19.18</v>
       </c>
       <c r="I69" s="5">
         <f>G69*H69</f>
@@ -4531,13 +4519,13 @@
         <v/>
       </c>
       <c r="K69" s="5" t="n">
-        <v>23.18</v>
+        <v>21.94</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>23.18</v>
+        <v>19.59</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>23.18</v>
+        <v>21.15666666666667</v>
       </c>
       <c r="N69" s="6">
         <f>J69/M69-1</f>
@@ -4549,37 +4537,37 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>310061</v>
+        <v>616351</v>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>7897411610750</t>
+          <t>7897947612594</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>LACTULONA 667MG/ML XPE FR 120ML SB AMEIXA</t>
+          <t>LAVITAN VIT AZ MULHER COMP REV FR C/ 90</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>46.8384</v>
+        <v>22.22</v>
       </c>
       <c r="I70" s="5">
         <f>G70*H70</f>
@@ -4590,13 +4578,13 @@
         <v/>
       </c>
       <c r="K70" s="5" t="n">
-        <v>48.17</v>
+        <v>21.39</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>42.12</v>
+        <v>21.39</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>45.98166666666666</v>
+        <v>21.39</v>
       </c>
       <c r="N70" s="6">
         <f>J70/M70-1</f>
@@ -4608,24 +4596,24 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.9% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>984</v>
+        <v>646341</v>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>7897947621077</t>
+          <t>7908615053097</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN COMPLEXO B COMP REV FR X 100</t>
+          <t>LEAVE IN ELSEVE 100ML CICATRI RENOV BNGA</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -4638,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>38.97</v>
+        <v>26.54</v>
       </c>
       <c r="I71" s="5">
         <f>G71*H71</f>
@@ -4648,44 +4636,56 @@
         <f>H71/E71</f>
         <v/>
       </c>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="6" t="n"/>
-      <c r="O71" s="6" t="n"/>
+      <c r="K71" s="5" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="N71" s="6">
+        <f>J71/M71-1</f>
+        <v/>
+      </c>
+      <c r="O71" s="6">
+        <f>J71/K71-1</f>
+        <v/>
+      </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>564641</v>
+        <v>640591</v>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>7897947601147</t>
+          <t>7898040322540</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN MELATONINA 0,21MG CP PT 90 MOR</t>
+          <t>MARESIS (N.S.) SOL SPRAY FR 100ML</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>19.18</v>
+        <v>37.7427</v>
       </c>
       <c r="I72" s="5">
         <f>G72*H72</f>
@@ -4696,13 +4696,13 @@
         <v/>
       </c>
       <c r="K72" s="5" t="n">
-        <v>21.94</v>
+        <v>41.6</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>19.59</v>
+        <v>37.585</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>21.15666666666667</v>
+        <v>40.26166666666666</v>
       </c>
       <c r="N72" s="6">
         <f>J72/M72-1</f>
@@ -4721,30 +4721,30 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>616351</v>
+        <v>665751</v>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>7897947612594</t>
+          <t>7896148500600</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN VIT AZ MULHER COMP REV FR C/ 90</t>
+          <t>MEL DE ABELHA 200G BISNAGA FITOBEL</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>22.22</v>
+        <v>10.54</v>
       </c>
       <c r="I73" s="5">
         <f>G73*H73</f>
@@ -4755,13 +4755,13 @@
         <v/>
       </c>
       <c r="K73" s="5" t="n">
-        <v>21.39</v>
+        <v>10.54</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>21.39</v>
+        <v>9.43</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>21.39</v>
+        <v>10.17</v>
       </c>
       <c r="N73" s="6">
         <f>J73/M73-1</f>
@@ -4773,37 +4773,37 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.9% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>646341</v>
+        <v>345701</v>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>7908615053097</t>
+          <t>7896014669028</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>LEAVE IN ELSEVE 100ML CICATRI RENOV BNGA</t>
+          <t>METREXATO 2,5MG CX 24 COMP</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>26.54</v>
+        <v>25.110068</v>
       </c>
       <c r="I74" s="5">
         <f>G74*H74</f>
@@ -4814,13 +4814,13 @@
         <v/>
       </c>
       <c r="K74" s="5" t="n">
-        <v>30.07</v>
+        <v>24.8467</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>30.07</v>
+        <v>20.995</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>30.07</v>
+        <v>23.38833333333334</v>
       </c>
       <c r="N74" s="6">
         <f>J74/M74-1</f>
@@ -4832,37 +4832,37 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>640591</v>
+        <v>650421</v>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>7898040322540</t>
+          <t>7891800666090</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>MARESIS (N.S.) SOL SPRAY FR 100ML</t>
+          <t>MICROPOROSA CREMER BRANCA 2,5CMX90CM</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>37.7427</v>
+        <v>3.9382</v>
       </c>
       <c r="I75" s="5">
         <f>G75*H75</f>
@@ -4873,13 +4873,13 @@
         <v/>
       </c>
       <c r="K75" s="5" t="n">
-        <v>41.6</v>
+        <v>4.0517</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>37.585</v>
+        <v>3.83</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>40.26166666666666</v>
+        <v>3.9778</v>
       </c>
       <c r="N75" s="6">
         <f>J75/M75-1</f>
@@ -4898,30 +4898,30 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>665751</v>
+        <v>229001</v>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>7896148500600</t>
+          <t>7896212429738</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>MEL DE ABELHA 200G BISNAGA FITOBEL</t>
+          <t>MOTILIUM 10MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>10.54</v>
+        <v>27.88</v>
       </c>
       <c r="I76" s="5">
         <f>G76*H76</f>
@@ -4932,13 +4932,13 @@
         <v/>
       </c>
       <c r="K76" s="5" t="n">
-        <v>10.54</v>
+        <v>28.63</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>9.43</v>
+        <v>27.02</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>10.17</v>
+        <v>27.89666666666666</v>
       </c>
       <c r="N76" s="6">
         <f>J76/M76-1</f>
@@ -4953,34 +4953,38 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (1 un); preços divergentes entre EANs (usado menor)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>345701</v>
+        <v>661311</v>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>7896014669028</t>
+          <t>0618231034291</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>METREXATO 2,5MG CX 24 COMP</t>
+          <t>MULTIVITALE VIT D 2.000UI 60CPS</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>25.110068</v>
+        <v>18.31</v>
       </c>
       <c r="I77" s="5">
         <f>G77*H77</f>
@@ -4991,13 +4995,13 @@
         <v/>
       </c>
       <c r="K77" s="5" t="n">
-        <v>24.8467</v>
+        <v>18.31</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>20.995</v>
+        <v>18.31</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>23.38833333333334</v>
+        <v>18.31</v>
       </c>
       <c r="N77" s="6">
         <f>J77/M77-1</f>
@@ -5009,37 +5013,37 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>650421</v>
+        <v>651901</v>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>7891800666090</t>
+          <t>7898108640050</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>MICROPOROSA CREMER BRANCA 2,5CMX90CM</t>
+          <t>N COMPRESSA GAZES 11FIOS ESTER 5UND   SANF %DN:0.00</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>3.9382</v>
+        <v>0.8929999999999999</v>
       </c>
       <c r="I78" s="5">
         <f>G78*H78</f>
@@ -5050,13 +5054,13 @@
         <v/>
       </c>
       <c r="K78" s="5" t="n">
-        <v>4.0517</v>
+        <v>0.92</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>3.83</v>
+        <v>0.92</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>3.9778</v>
+        <v>0.92</v>
       </c>
       <c r="N78" s="6">
         <f>J78/M78-1</f>
@@ -5075,30 +5079,30 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>229001</v>
+        <v>669941</v>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>7896212429738</t>
+          <t>7506306255678</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>MOTILIUM 10MG CX 30 COMP</t>
+          <t>N SAB DOVE ESFOLIANTE BEAUTY SCRUB COCO 280G   UNIL %DN:0.00</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>27.88</v>
+        <v>38.79</v>
       </c>
       <c r="I79" s="5">
         <f>G79*H79</f>
@@ -5109,13 +5113,13 @@
         <v/>
       </c>
       <c r="K79" s="5" t="n">
-        <v>28.63</v>
+        <v>37.43</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>27.02</v>
+        <v>37.43</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>27.89666666666666</v>
+        <v>37.43</v>
       </c>
       <c r="N79" s="6">
         <f>J79/M79-1</f>
@@ -5127,41 +5131,37 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un); preços divergentes entre EANs (usado menor)</t>
-        </is>
-      </c>
+          <t>REAJUSTE +3.6% vs últ. (≤4%)</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>661311</v>
+        <v>556401</v>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>0618231034291</t>
+          <t>7896677704890</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>MULTIVITALE VIT D 2.000UI 60CPS</t>
+          <t>NERVOCALM 250MG CX 20 COMP</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>18.31</v>
+        <v>30.15</v>
       </c>
       <c r="I80" s="5">
         <f>G80*H80</f>
@@ -5172,13 +5172,13 @@
         <v/>
       </c>
       <c r="K80" s="5" t="n">
-        <v>18.31</v>
+        <v>31.33</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>18.31</v>
+        <v>22.32</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>18.31</v>
+        <v>28.32666666666666</v>
       </c>
       <c r="N80" s="6">
         <f>J80/M80-1</f>
@@ -5197,30 +5197,30 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>651901</v>
+        <v>358321</v>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>7898108640050</t>
+          <t>7894916500333</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N COMPRESSA GAZES 11FIOS ESTER 5UND   SANF %DN:0.00</t>
+          <t>NEUTROFER 300MG FR 30 COMP</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.8929999999999999</v>
+        <v>47.21925</v>
       </c>
       <c r="I81" s="5">
         <f>G81*H81</f>
@@ -5231,13 +5231,13 @@
         <v/>
       </c>
       <c r="K81" s="5" t="n">
-        <v>0.92</v>
+        <v>45.04</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.92</v>
+        <v>44.905</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.92</v>
+        <v>44.995</v>
       </c>
       <c r="N81" s="6">
         <f>J81/M81-1</f>
@@ -5249,24 +5249,24 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +4.9% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>669941</v>
+        <v>443</v>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>7506306255678</t>
+          <t>7891010704490</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N SAB DOVE ESFOLIANTE BEAUTY SCRUB COCO 280G   UNIL %DN:0.00</t>
+          <t>NEUTROG D CLEAN ESF ENER 100G</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -5279,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>38.79</v>
+        <v>33.46</v>
       </c>
       <c r="I82" s="5">
         <f>G82*H82</f>
@@ -5290,13 +5290,13 @@
         <v/>
       </c>
       <c r="K82" s="5" t="n">
-        <v>37.43</v>
+        <v>33.105</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>37.43</v>
+        <v>33.105</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>37.43</v>
+        <v>33.105</v>
       </c>
       <c r="N82" s="6">
         <f>J82/M82-1</f>
@@ -5308,37 +5308,37 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.6% vs últ. (≤4%)</t>
+          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>556401</v>
+        <v>563181</v>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>7896677704890</t>
+          <t>7896523224435</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>NERVOCALM 250MG CX 20 COMP</t>
+          <t>OLEO MINERAL FR 100 ML</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>30.15</v>
+        <v>7.2</v>
       </c>
       <c r="I83" s="5">
         <f>G83*H83</f>
@@ -5349,13 +5349,13 @@
         <v/>
       </c>
       <c r="K83" s="5" t="n">
-        <v>31.33</v>
+        <v>6.99</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>22.32</v>
+        <v>6.99</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>28.32666666666666</v>
+        <v>6.989999999999999</v>
       </c>
       <c r="N83" s="6">
         <f>J83/M83-1</f>
@@ -5367,37 +5367,37 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>358321</v>
+        <v>609511</v>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>7894916500333</t>
+          <t>7897316806388</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>NEUTROFER 300MG FR 30 COMP</t>
+          <t>OPTIVE FR 15ML</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>47.21925</v>
+        <v>65.136</v>
       </c>
       <c r="I84" s="5">
         <f>G84*H84</f>
@@ -5408,13 +5408,13 @@
         <v/>
       </c>
       <c r="K84" s="5" t="n">
-        <v>45.04</v>
+        <v>81.22</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>44.905</v>
+        <v>73.28</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>44.995</v>
+        <v>78.57333333333334</v>
       </c>
       <c r="N84" s="6">
         <f>J84/M84-1</f>
@@ -5426,37 +5426,37 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.9% vs média (≤6%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>443</v>
+        <v>630971</v>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>7891010704490</t>
+          <t>7896902209749</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>NEUTROG D CLEAN ESF ENER 100G</t>
+          <t>PEDRA HUME FARMAX 30ML C/GLIC SPRAY</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>33.46</v>
+        <v>7.04</v>
       </c>
       <c r="I85" s="5">
         <f>G85*H85</f>
@@ -5467,13 +5467,13 @@
         <v/>
       </c>
       <c r="K85" s="5" t="n">
-        <v>33.105</v>
+        <v>7.04</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>33.105</v>
+        <v>7.04</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>33.105</v>
+        <v>7.04</v>
       </c>
       <c r="N85" s="6">
         <f>J85/M85-1</f>
@@ -5485,37 +5485,37 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>563181</v>
+        <v>319641</v>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>7896523224435</t>
+          <t>7891058003562</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>OLEO MINERAL FR 100 ML</t>
+          <t>PURAN T4 37,5MCG CX 30 COMP</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>7.2</v>
+        <v>8.487500000000001</v>
       </c>
       <c r="I86" s="5">
         <f>G86*H86</f>
@@ -5526,13 +5526,13 @@
         <v/>
       </c>
       <c r="K86" s="5" t="n">
-        <v>6.99</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>6.99</v>
+        <v>7.6</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>6.989999999999999</v>
+        <v>7.988333333333334</v>
       </c>
       <c r="N86" s="6">
         <f>J86/M86-1</f>
@@ -5544,37 +5544,37 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
+          <t>REAJUSTE +2.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>609511</v>
+        <v>604551</v>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>7897316806388</t>
+          <t>7891010253691</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>OPTIVE FR 15ML</t>
+          <t>PV - SAB.LIQ.JOHN.K.200ML LIMP.S.PO</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>65.136</v>
+        <v>19.5</v>
       </c>
       <c r="I87" s="5">
         <f>G87*H87</f>
@@ -5585,13 +5585,13 @@
         <v/>
       </c>
       <c r="K87" s="5" t="n">
-        <v>81.22</v>
+        <v>19.5333</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>73.28</v>
+        <v>19.5333</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>78.57333333333334</v>
+        <v>19.5333</v>
       </c>
       <c r="N87" s="6">
         <f>J87/M87-1</f>
@@ -5606,34 +5606,38 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (1 un)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>630971</v>
+        <v>662901</v>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>7896902209749</t>
+          <t>7897947619548</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>PEDRA HUME FARMAX 30ML C/GLIC SPRAY</t>
+          <t>PVV - LAVITAN OMEGA COMPLEX CAP GEL PT X 30 SF</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>7.04</v>
+        <v>50.46</v>
       </c>
       <c r="I88" s="5">
         <f>G88*H88</f>
@@ -5643,56 +5647,44 @@
         <f>H88/E88</f>
         <v/>
       </c>
-      <c r="K88" s="5" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="N88" s="6">
-        <f>J88/M88-1</f>
-        <v/>
-      </c>
-      <c r="O88" s="6">
-        <f>J88/K88-1</f>
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="6" t="n"/>
+      <c r="O88" s="6" t="n"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>319641</v>
+        <v>598361</v>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>7891058003562</t>
+          <t>7896902201255</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PURAN T4 37,5MCG CX 30 COMP</t>
+          <t>REMOV ESM FARMAX 100ML S/ACET VITAM</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>8.487500000000001</v>
+        <v>3.79</v>
       </c>
       <c r="I89" s="5">
         <f>G89*H89</f>
@@ -5703,13 +5695,13 @@
         <v/>
       </c>
       <c r="K89" s="5" t="n">
-        <v>8.255000000000001</v>
+        <v>4.56</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>7.6</v>
+        <v>4.56</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>7.988333333333334</v>
+        <v>4.56</v>
       </c>
       <c r="N89" s="6">
         <f>J89/M89-1</f>
@@ -5721,37 +5713,37 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.8% vs últ. (≤4%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>604551</v>
+        <v>607761</v>
       </c>
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>7891010253691</t>
+          <t>7894650009567</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>PV - SAB.LIQ.JOHN.K.200ML LIMP.S.PO</t>
+          <t>REP OFF FAMILY SPRAY 170ML</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
       <c r="I90" s="5">
         <f>G90*H90</f>
@@ -5762,13 +5754,13 @@
         <v/>
       </c>
       <c r="K90" s="5" t="n">
-        <v>19.5333</v>
+        <v>18.38</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>19.5333</v>
+        <v>18.38</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>19.5333</v>
+        <v>18.38</v>
       </c>
       <c r="N90" s="6">
         <f>J90/M90-1</f>
@@ -5783,38 +5775,34 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un)</t>
-        </is>
-      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>662901</v>
+        <v>544781</v>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>7897947619548</t>
+          <t>7894650005712</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>PVV - LAVITAN OMEGA COMPLEX CAP GEL PT X 30 SF</t>
+          <t>REP OFF KIDS LOCAO 117ML</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>50.46</v>
+        <v>19.84</v>
       </c>
       <c r="I91" s="5">
         <f>G91*H91</f>
@@ -5824,44 +5812,56 @@
         <f>H91/E91</f>
         <v/>
       </c>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="n"/>
-      <c r="M91" s="5" t="n"/>
-      <c r="N91" s="6" t="n"/>
-      <c r="O91" s="6" t="n"/>
+      <c r="K91" s="5" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="N91" s="6">
+        <f>J91/M91-1</f>
+        <v/>
+      </c>
+      <c r="O91" s="6">
+        <f>J91/K91-1</f>
+        <v/>
+      </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>598361</v>
+        <v>623921</v>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>7896902201255</t>
+          <t>7509546678832</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>REMOV ESM FARMAX 100ML S/ACET VITAM</t>
+          <t>SAB BARRA PROTEX CARVAO 85G</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>3.79</v>
+        <v>3.55</v>
       </c>
       <c r="I92" s="5">
         <f>G92*H92</f>
@@ -5872,13 +5872,13 @@
         <v/>
       </c>
       <c r="K92" s="5" t="n">
-        <v>4.56</v>
+        <v>3.75</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>4.56</v>
+        <v>3.75</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>4.56</v>
+        <v>3.75</v>
       </c>
       <c r="N92" s="6">
         <f>J92/M92-1</f>
@@ -5897,30 +5897,30 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>607761</v>
+        <v>843</v>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>7894650009567</t>
+          <t>7891010781668</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>REP OFF FAMILY SPRAY 170ML</t>
+          <t>SAB J J BABY HORA DO SONO 80G</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>17.2</v>
+        <v>5.63</v>
       </c>
       <c r="I93" s="5">
         <f>G93*H93</f>
@@ -5931,13 +5931,13 @@
         <v/>
       </c>
       <c r="K93" s="5" t="n">
-        <v>18.38</v>
+        <v>5.79</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>18.38</v>
+        <v>5.79</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>18.38</v>
+        <v>5.79</v>
       </c>
       <c r="N93" s="6">
         <f>J93/M93-1</f>
@@ -5956,30 +5956,30 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>544781</v>
+        <v>571261</v>
       </c>
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>7894650005712</t>
+          <t>7891024027257</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>REP OFF KIDS LOCAO 117ML</t>
+          <t>SAB LIQ PROTEX 200ML REF VIT E</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>19.84</v>
+        <v>7.75</v>
       </c>
       <c r="I94" s="5">
         <f>G94*H94</f>
@@ -5990,13 +5990,13 @@
         <v/>
       </c>
       <c r="K94" s="5" t="n">
-        <v>20.92</v>
+        <v>7.59</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>20.92</v>
+        <v>7.31</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>20.92</v>
+        <v>7.496666666666666</v>
       </c>
       <c r="N94" s="6">
         <f>J94/M94-1</f>
@@ -6008,37 +6008,37 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +2.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>623921</v>
+        <v>623971</v>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>7509546678832</t>
+          <t>7509546665986</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>SAB BARRA PROTEX CARVAO 85G</t>
+          <t>SAB LIQ PROTEX PUM ERVA DOCE 400ML</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>3.55</v>
+        <v>16.67</v>
       </c>
       <c r="I95" s="5">
         <f>G95*H95</f>
@@ -6049,13 +6049,13 @@
         <v/>
       </c>
       <c r="K95" s="5" t="n">
-        <v>3.75</v>
+        <v>19.53</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>3.75</v>
+        <v>19.53</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>3.75</v>
+        <v>19.53</v>
       </c>
       <c r="N95" s="6">
         <f>J95/M95-1</f>
@@ -6074,30 +6074,30 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>843</v>
+        <v>689301</v>
       </c>
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>7891010781668</t>
+          <t>7891150083042</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>SAB J J BABY HORA DO SONO 80G</t>
+          <t>SAB LIQ REXONA ANTIBAC FRESH 250ML</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>5.63</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I96" s="5">
         <f>G96*H96</f>
@@ -6108,13 +6108,13 @@
         <v/>
       </c>
       <c r="K96" s="5" t="n">
-        <v>5.79</v>
+        <v>9.58</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>5.79</v>
+        <v>9.58</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>5.79</v>
+        <v>9.58</v>
       </c>
       <c r="N96" s="6">
         <f>J96/M96-1</f>
@@ -6133,30 +6133,30 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>571261</v>
+        <v>598481</v>
       </c>
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>7891024027257</t>
+          <t>7891024035313</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ PROTEX 200ML REF VIT E</t>
+          <t>SAB PROTEX MEN SPORT 85G</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="I97" s="5">
         <f>G97*H97</f>
@@ -6167,13 +6167,13 @@
         <v/>
       </c>
       <c r="K97" s="5" t="n">
-        <v>7.59</v>
+        <v>35.535</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>7.31</v>
+        <v>35.535</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>7.496666666666666</v>
+        <v>35.535</v>
       </c>
       <c r="N97" s="6">
         <f>J97/M97-1</f>
@@ -6185,37 +6185,41 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.1% vs últ. (≤4%)</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>conferir emb.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>623971</v>
+        <v>545341</v>
       </c>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>7509546665986</t>
+          <t>7896018700789</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ PROTEX PUM ERVA DOCE 400ML</t>
+          <t>SABONETE INFANTIL BARRA CHÁ DE CAMOMILA DISNEY BABY HUGGIES 75G</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>16.67</v>
+        <v>4.55</v>
       </c>
       <c r="I98" s="5">
         <f>G98*H98</f>
@@ -6226,13 +6230,13 @@
         <v/>
       </c>
       <c r="K98" s="5" t="n">
-        <v>19.53</v>
+        <v>4.55</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>19.53</v>
+        <v>4.55</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>19.53</v>
+        <v>4.55</v>
       </c>
       <c r="N98" s="6">
         <f>J98/M98-1</f>
@@ -6251,17 +6255,17 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>689301</v>
+        <v>672851</v>
       </c>
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>7891150083042</t>
+          <t>7891150097643</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>SAB LIQ REXONA ANTIBAC FRESH 250ML</t>
+          <t>SH DOVE BOND 350ML+COND 150ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -6274,7 +6278,7 @@
         <v>2</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>21.52</v>
       </c>
       <c r="I99" s="5">
         <f>G99*H99</f>
@@ -6285,13 +6289,13 @@
         <v/>
       </c>
       <c r="K99" s="5" t="n">
-        <v>9.58</v>
+        <v>32.18</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>9.58</v>
+        <v>32.18</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>9.58</v>
+        <v>32.18</v>
       </c>
       <c r="N99" s="6">
         <f>J99/M99-1</f>
@@ -6310,30 +6314,30 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>598481</v>
+        <v>672151</v>
       </c>
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>7891024035313</t>
+          <t>7908966528404</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>SAB PROTEX MEN SPORT 85G</t>
+          <t>SH ELSEVE COLAGENO 200ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>3.55</v>
+        <v>14.37</v>
       </c>
       <c r="I100" s="5">
         <f>G100*H100</f>
@@ -6344,13 +6348,13 @@
         <v/>
       </c>
       <c r="K100" s="5" t="n">
-        <v>35.535</v>
+        <v>14.9</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>35.535</v>
+        <v>12.96</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>35.535</v>
+        <v>12.96</v>
       </c>
       <c r="N100" s="6">
         <f>J100/M100-1</f>
@@ -6365,38 +6369,34 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>conferir emb.</t>
-        </is>
-      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>545341</v>
+        <v>635261</v>
       </c>
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>7896018700789</t>
+          <t>7891033535026</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>SABONETE INFANTIL BARRA CHÁ DE CAMOMILA DISNEY BABY HUGGIES 75G</t>
+          <t>SIAGE SH ACELERA CRESCIMENTO 250ML</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>4.55</v>
+        <v>40.7</v>
       </c>
       <c r="I101" s="5">
         <f>G101*H101</f>
@@ -6407,13 +6407,13 @@
         <v/>
       </c>
       <c r="K101" s="5" t="n">
-        <v>4.55</v>
+        <v>42.58</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>4.55</v>
+        <v>42.58</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>4.55</v>
+        <v>42.58</v>
       </c>
       <c r="N101" s="6">
         <f>J101/M101-1</f>
@@ -6432,30 +6432,30 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>672851</v>
+        <v>605291</v>
       </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>7891150097643</t>
+          <t>7897460401934</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>SH DOVE BOND 350ML+COND 150ML-DEMAIS PROD</t>
+          <t>SILIMALON 100+70MG CX 10 COMP REV</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>21.52</v>
+        <v>18.729</v>
       </c>
       <c r="I102" s="5">
         <f>G102*H102</f>
@@ -6466,13 +6466,13 @@
         <v/>
       </c>
       <c r="K102" s="5" t="n">
-        <v>32.18</v>
+        <v>19.2467</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>32.18</v>
+        <v>15.4333</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>32.18</v>
+        <v>17.66546666666667</v>
       </c>
       <c r="N102" s="6">
         <f>J102/M102-1</f>
@@ -6491,30 +6491,30 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>672151</v>
+        <v>434001</v>
       </c>
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>7908966528404</t>
+          <t>7897460401743</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>SH ELSEVE COLAGENO 200ML-DEMAIS PROD</t>
+          <t>SILIMALON 140 140+100MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>14.37</v>
+        <v>89.982</v>
       </c>
       <c r="I103" s="5">
         <f>G103*H103</f>
@@ -6525,13 +6525,13 @@
         <v/>
       </c>
       <c r="K103" s="5" t="n">
-        <v>14.9</v>
+        <v>92.47</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>12.96</v>
+        <v>84.03</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>12.96</v>
+        <v>88.16223333333335</v>
       </c>
       <c r="N103" s="6">
         <f>J103/M103-1</f>
@@ -6550,30 +6550,30 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>635261</v>
+        <v>529941</v>
       </c>
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>7891033535026</t>
+          <t>7908134200552</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>SIAGE SH ACELERA CRESCIMENTO 250ML</t>
+          <t>SLINDA 4MG (CAIXA C/ 3 CARTELAS) C/28 COMP REV</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>40.7</v>
+        <v>219.2827</v>
       </c>
       <c r="I104" s="5">
         <f>G104*H104</f>
@@ -6584,13 +6584,13 @@
         <v/>
       </c>
       <c r="K104" s="5" t="n">
-        <v>42.58</v>
+        <v>226.51</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>42.58</v>
+        <v>67.41330000000001</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>42.58</v>
+        <v>121.7522</v>
       </c>
       <c r="N104" s="6">
         <f>J104/M104-1</f>
@@ -6609,30 +6609,30 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>605291</v>
+        <v>529921</v>
       </c>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>7897460401934</t>
+          <t>7908134200453</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 100+70MG CX 10 COMP REV</t>
+          <t>SLINDA 4MG CX 24 COMP REV+4 PLACEBOS</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>18.729</v>
+        <v>92.04650000000001</v>
       </c>
       <c r="I105" s="5">
         <f>G105*H105</f>
@@ -6643,13 +6643,13 @@
         <v/>
       </c>
       <c r="K105" s="5" t="n">
-        <v>19.2467</v>
+        <v>95.08</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>15.4333</v>
+        <v>89.83499999999999</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>17.66546666666667</v>
+        <v>91.58333333333333</v>
       </c>
       <c r="N105" s="6">
         <f>J105/M105-1</f>
@@ -6668,30 +6668,30 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>434001</v>
+        <v>558381</v>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>7897460401743</t>
+          <t>7896902212152</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>SILIMALON 140 140+100MG CX 30 COMP REV</t>
+          <t>SOLUCAO SORIMAX 100 ML</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>89.982</v>
+        <v>2.39</v>
       </c>
       <c r="I106" s="5">
         <f>G106*H106</f>
@@ -6702,13 +6702,13 @@
         <v/>
       </c>
       <c r="K106" s="5" t="n">
-        <v>92.47</v>
+        <v>2.69</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>84.03</v>
+        <v>2.69</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>88.16223333333335</v>
+        <v>2.69</v>
       </c>
       <c r="N106" s="6">
         <f>J106/M106-1</f>
@@ -6727,30 +6727,30 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>529941</v>
+        <v>661151</v>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>7908134200552</t>
+          <t>7899852025469</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>SLINDA 4MG (CAIXA C/ 3 CARTELAS) C/28 COMP REV</t>
+          <t>SPR VULT RECARGA HIDRT 100ML-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>219.2827</v>
+        <v>27.38</v>
       </c>
       <c r="I107" s="5">
         <f>G107*H107</f>
@@ -6761,13 +6761,13 @@
         <v/>
       </c>
       <c r="K107" s="5" t="n">
-        <v>226.51</v>
+        <v>27.51</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>67.41330000000001</v>
+        <v>27.51</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>121.7522</v>
+        <v>27.51</v>
       </c>
       <c r="N107" s="6">
         <f>J107/M107-1</f>
@@ -6786,30 +6786,30 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>529921</v>
+        <v>624141</v>
       </c>
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>7908134200453</t>
+          <t>7506339305142</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>SLINDA 4MG CX 24 COMP REV+4 PLACEBOS</t>
+          <t>TESTE GRAV CLEARBLUE PLUS 2UNI-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>92.04650000000001</v>
+        <v>23.84</v>
       </c>
       <c r="I108" s="5">
         <f>G108*H108</f>
@@ -6820,13 +6820,13 @@
         <v/>
       </c>
       <c r="K108" s="5" t="n">
-        <v>95.08</v>
+        <v>24.7675</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>89.83499999999999</v>
+        <v>23.11</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>91.58333333333333</v>
+        <v>24.215</v>
       </c>
       <c r="N108" s="6">
         <f>J108/M108-1</f>
@@ -6845,30 +6845,30 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>558381</v>
+        <v>622921</v>
       </c>
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>7896902212152</t>
+          <t>7500435137959</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>SOLUCAO SORIMAX 100 ML</t>
+          <t>TESTE GRAV CLEARBLUE SAIBA ANTES-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>2.39</v>
+        <v>18.753</v>
       </c>
       <c r="I109" s="5">
         <f>G109*H109</f>
@@ -6879,13 +6879,13 @@
         <v/>
       </c>
       <c r="K109" s="5" t="n">
-        <v>2.69</v>
+        <v>21.65</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>2.69</v>
+        <v>19.62</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>2.69</v>
+        <v>20.60666666666667</v>
       </c>
       <c r="N109" s="6">
         <f>J109/M109-1</f>
@@ -6904,30 +6904,30 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>661151</v>
+        <v>610651</v>
       </c>
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>7899852025469</t>
+          <t>7908032300866</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>SPR VULT RECARGA HIDRT 100ML-DEMAIS PROD</t>
+          <t>TOALHAS UMED PIQUITUCHO PRATIC C/48UND</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>27.38</v>
+        <v>4.0255</v>
       </c>
       <c r="I110" s="5">
         <f>G110*H110</f>
@@ -6938,13 +6938,13 @@
         <v/>
       </c>
       <c r="K110" s="5" t="n">
-        <v>27.51</v>
+        <v>6.03</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>27.51</v>
+        <v>6.03</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>27.51</v>
+        <v>6.03</v>
       </c>
       <c r="N110" s="6">
         <f>J110/M110-1</f>
@@ -6963,30 +6963,30 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>624141</v>
+        <v>319341</v>
       </c>
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>7506339305142</t>
+          <t>7891045008433</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>TESTE GRAV CLEARBLUE PLUS 2UNI-DEMAIS PROD</t>
+          <t>V - NORDETTE 0,15+0,03MG CX 21 DRG</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>23.84</v>
+        <v>9.927499999999998</v>
       </c>
       <c r="I111" s="5">
         <f>G111*H111</f>
@@ -6997,13 +6997,13 @@
         <v/>
       </c>
       <c r="K111" s="5" t="n">
-        <v>24.7675</v>
+        <v>10.31</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>23.11</v>
+        <v>9.265000000000001</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>24.215</v>
+        <v>9.831666666666667</v>
       </c>
       <c r="N111" s="6">
         <f>J111/M111-1</f>
@@ -7022,30 +7022,30 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>622921</v>
+        <v>654331</v>
       </c>
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>7500435137959</t>
+          <t>7891653014260</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>TESTE GRAV CLEARBLUE SAIBA ANTES-DEMAIS PROD</t>
+          <t>VAGISIL DEO INTIMO JASMIN BRANCO 75ML</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>18.753</v>
+        <v>25.77</v>
       </c>
       <c r="I112" s="5">
         <f>G112*H112</f>
@@ -7056,13 +7056,13 @@
         <v/>
       </c>
       <c r="K112" s="5" t="n">
-        <v>21.65</v>
+        <v>24.47</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>19.62</v>
+        <v>24.47</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>20.60666666666667</v>
+        <v>24.47</v>
       </c>
       <c r="N112" s="6">
         <f>J112/M112-1</f>
@@ -7074,37 +7074,37 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>610651</v>
+        <v>662301</v>
       </c>
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>7908032300866</t>
+          <t>7891653014031</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>TOALHAS UMED PIQUITUCHO PRATIC C/48UND</t>
+          <t>VAGISIL DEO INTIMO ODOR BLOCK 60ML</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>4.0255</v>
+        <v>22.43</v>
       </c>
       <c r="I113" s="5">
         <f>G113*H113</f>
@@ -7115,13 +7115,13 @@
         <v/>
       </c>
       <c r="K113" s="5" t="n">
-        <v>6.03</v>
+        <v>22.43</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>6.03</v>
+        <v>22.42</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>6.03</v>
+        <v>22.42666666666667</v>
       </c>
       <c r="N113" s="6">
         <f>J113/M113-1</f>
@@ -7140,17 +7140,17 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>319341</v>
+        <v>654311</v>
       </c>
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>7891045008433</t>
+          <t>7891653040078</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>V - NORDETTE 0,15+0,03MG CX 21 DRG</t>
+          <t>VAGISIL SAB INTIMO URIN PROTECT 300ML</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -7163,7 +7163,7 @@
         <v>4</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>9.927499999999998</v>
+        <v>21.67</v>
       </c>
       <c r="I114" s="5">
         <f>G114*H114</f>
@@ -7174,13 +7174,13 @@
         <v/>
       </c>
       <c r="K114" s="5" t="n">
-        <v>10.31</v>
+        <v>21.68</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>9.265000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>9.831666666666667</v>
+        <v>20.43666666666667</v>
       </c>
       <c r="N114" s="6">
         <f>J114/M114-1</f>
@@ -7195,202 +7195,25 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>estoque parcial (1 un)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>654331</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr"/>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>7891653014260</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>VAGISIL DEO INTIMO JASMIN BRANCO 75ML</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="I115" s="5">
-        <f>G115*H115</f>
-        <v/>
-      </c>
-      <c r="J115" s="5">
-        <f>H115/E115</f>
-        <v/>
-      </c>
-      <c r="K115" s="5" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="L115" s="5" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="M115" s="5" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="N115" s="6">
-        <f>J115/M115-1</f>
-        <v/>
-      </c>
-      <c r="O115" s="6">
-        <f>J115/K115-1</f>
-        <v/>
-      </c>
-      <c r="P115" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +5.3% vs média (≤6%)</t>
-        </is>
-      </c>
-      <c r="Q115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>662301</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr"/>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>7891653014031</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>VAGISIL DEO INTIMO ODOR BLOCK 60ML</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="I116" s="5">
-        <f>G116*H116</f>
-        <v/>
-      </c>
-      <c r="J116" s="5">
-        <f>H116/E116</f>
-        <v/>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L116" s="5" t="n">
-        <v>22.42</v>
-      </c>
-      <c r="M116" s="5" t="n">
-        <v>22.42666666666667</v>
-      </c>
-      <c r="N116" s="6">
-        <f>J116/M116-1</f>
-        <v/>
-      </c>
-      <c r="O116" s="6">
-        <f>J116/K116-1</f>
-        <v/>
-      </c>
-      <c r="P116" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I115" s="8">
+        <f>SUM(I2:I114)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>654311</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr"/>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>7891653040078</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>VAGISIL SAB INTIMO URIN PROTECT 300ML</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G117" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>21.67</v>
-      </c>
-      <c r="I117" s="5">
-        <f>G117*H117</f>
-        <v/>
-      </c>
-      <c r="J117" s="5">
-        <f>H117/E117</f>
-        <v/>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>21.68</v>
-      </c>
-      <c r="L117" s="5" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="M117" s="5" t="n">
-        <v>20.43666666666667</v>
-      </c>
-      <c r="N117" s="6">
-        <f>J117/M117-1</f>
-        <v/>
-      </c>
-      <c r="O117" s="6">
-        <f>J117/K117-1</f>
-        <v/>
-      </c>
-      <c r="P117" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q117" s="2" t="inlineStr">
-        <is>
-          <t>estoque parcial (1 un)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I118" s="8">
-        <f>SUM(I2:I117)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>Pedido FINAL NAZARIA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
